--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O12">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P12">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P13">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE13">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G18">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE15">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O12">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P12">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O13">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU31"/>
+  <dimension ref="A1:AU35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G10">
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>5.35</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>8.1</v>
+        <v>2.91</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,16 +2304,16 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P13">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE13">
         <v>0</v>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>3.71</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="P14">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.55</v>
+        <v>2.37</v>
       </c>
       <c r="O15">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-10 14:30:00</t>
+          <t>2026-08-10 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-10 15:00:00</t>
+          <t>2026-08-10 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-10 15:15:00</t>
+          <t>2026-08-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-10 15:30:00</t>
+          <t>2026-08-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-10 15:30:00</t>
+          <t>2026-08-10 15:15:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-10 16:00:00</t>
+          <t>2026-08-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-10 16:00:00</t>
+          <t>2026-08-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:00</t>
+          <t>2026-08-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:00</t>
+          <t>2026-08-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-10 18:30:00</t>
+          <t>2026-08-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-10 19:30:00</t>
+          <t>2026-08-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-10 21:00:00</t>
+          <t>2026-08-10 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,156 +5315,808 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>2.1</v>
+      </c>
+      <c r="O33">
+        <v>2.5</v>
+      </c>
+      <c r="P33">
+        <v>4.5</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>2.87</v>
+      </c>
+      <c r="AB33">
+        <v>1.4</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Deportivo Cuenca</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-08-10 21:00:00</t>
         </is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G10">
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G11">
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O13">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O14">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P14">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P13">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2473,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O14">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P14">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q27">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU35"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,34 +644,34 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA2">
         <v>1.93</v>
@@ -680,19 +680,19 @@
         <v>1.76</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>3.3</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2926,40 +2926,40 @@
         <v>1.82</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC16">
         <v>1.8</v>
@@ -2968,13 +2968,13 @@
         <v>1.93</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G21">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.44</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>4.44</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:00:00</t>
+          <t>2026-08-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="O27">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="P27">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.19</v>
+        <v>4.41</v>
       </c>
       <c r="O28">
-        <v>3.38</v>
+        <v>3.72</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AB28">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:00</t>
+          <t>2026-08-10 18:30:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-10 18:30:00</t>
+          <t>2026-08-10 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-10 19:30:00</t>
+          <t>2026-08-10 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 21:00:00</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5954,169 +5954,6 @@
         <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
-        <is>
-          <t>2026-08-10 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-08-10 21:00:00</t>
         </is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q11">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.91</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA12">
         <v>1.83</v>
@@ -2310,19 +2310,19 @@
         <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,40 +2437,40 @@
         <v>8.1</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC13">
         <v>1.98</v>
@@ -2479,13 +2479,13 @@
         <v>1.83</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>1.88</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,31 +831,31 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>1.76</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q10">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
+        <v>1.06</v>
+      </c>
+      <c r="Y10">
+        <v>1.27</v>
+      </c>
+      <c r="Z10">
+        <v>3.14</v>
+      </c>
+      <c r="AA10">
+        <v>2.05</v>
+      </c>
+      <c r="AB10">
+        <v>1.72</v>
+      </c>
+      <c r="AC10">
+        <v>3.51</v>
+      </c>
+      <c r="AD10">
+        <v>1.28</v>
+      </c>
+      <c r="AE10">
         <v>1.04</v>
       </c>
-      <c r="Y10">
-        <v>1.22</v>
-      </c>
-      <c r="Z10">
-        <v>3.75</v>
-      </c>
-      <c r="AA10">
+      <c r="AF10">
         <v>1.75</v>
       </c>
-      <c r="AB10">
+      <c r="AG10">
         <v>1.95</v>
       </c>
-      <c r="AC10">
-        <v>2.9</v>
-      </c>
-      <c r="AD10">
-        <v>1.36</v>
-      </c>
-      <c r="AE10">
-        <v>1.13</v>
-      </c>
-      <c r="AF10">
-        <v>1.62</v>
-      </c>
-      <c r="AG10">
-        <v>2.2</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O11">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA27">
         <v>2.15</v>
@@ -4755,19 +4755,19 @@
         <v>1.62</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,34 +5045,34 @@
         <v>4.78</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA29">
         <v>2.1</v>
@@ -5081,19 +5081,19 @@
         <v>1.63</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL29">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O13">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P13">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="R13">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
+        <v>1.22</v>
+      </c>
+      <c r="T13">
+        <v>3.34</v>
+      </c>
+      <c r="U13">
+        <v>2.25</v>
+      </c>
+      <c r="V13">
+        <v>1.57</v>
+      </c>
+      <c r="W13">
+        <v>1.11</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>1.13</v>
+      </c>
+      <c r="Z13">
+        <v>4.6</v>
+      </c>
+      <c r="AA13">
+        <v>1.5</v>
+      </c>
+      <c r="AB13">
+        <v>2.4</v>
+      </c>
+      <c r="AC13">
+        <v>2.33</v>
+      </c>
+      <c r="AD13">
+        <v>1.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.19</v>
+      </c>
+      <c r="AF13">
+        <v>1.5</v>
+      </c>
+      <c r="AG13">
+        <v>2.42</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.18</v>
+      </c>
+      <c r="AK13">
         <v>1.24</v>
-      </c>
-      <c r="T13">
-        <v>3.5</v>
-      </c>
-      <c r="U13">
-        <v>1.91</v>
-      </c>
-      <c r="V13">
-        <v>1.8</v>
-      </c>
-      <c r="W13">
-        <v>1.17</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.1</v>
-      </c>
-      <c r="Z13">
-        <v>6.05</v>
-      </c>
-      <c r="AA13">
-        <v>1.34</v>
-      </c>
-      <c r="AB13">
-        <v>3</v>
-      </c>
-      <c r="AC13">
-        <v>1.98</v>
-      </c>
-      <c r="AD13">
-        <v>1.83</v>
-      </c>
-      <c r="AE13">
-        <v>1.32</v>
-      </c>
-      <c r="AF13">
-        <v>1.6</v>
-      </c>
-      <c r="AG13">
-        <v>2.11</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.1</v>
-      </c>
-      <c r="AK13">
-        <v>3.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O14">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P14">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>4.6</v>
+        <v>6.05</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AB14">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AC14">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG14">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -3101,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
         <v>0</v>
@@ -3113,31 +3113,31 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>4.6</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA18">
         <v>2.7</v>
@@ -3288,19 +3288,19 @@
         <v>1.44</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O20">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB20">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-10 15:15:00</t>
+          <t>2026-08-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-10 15:30:00</t>
+          <t>2026-08-10 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.44</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q24">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.49</v>
+        <v>4.44</v>
       </c>
       <c r="O25">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB25">
         <v>1.78</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-10 16:00:00</t>
+          <t>2026-08-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="O26">
-        <v>4.33</v>
+        <v>3.07</v>
       </c>
       <c r="P26">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:00</t>
+          <t>2026-08-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="O27">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q27">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="T27">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="U27">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="Z27">
-        <v>2.73</v>
+        <v>11</v>
       </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="AB27">
+        <v>4</v>
+      </c>
+      <c r="AC27">
+        <v>1.5</v>
+      </c>
+      <c r="AD27">
+        <v>2.4</v>
+      </c>
+      <c r="AE27">
         <v>1.62</v>
       </c>
-      <c r="AC27">
-        <v>3.8</v>
-      </c>
-      <c r="AD27">
-        <v>1.2</v>
-      </c>
-      <c r="AE27">
-        <v>1.04</v>
-      </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.41</v>
+        <v>2.19</v>
       </c>
       <c r="O28">
-        <v>3.72</v>
+        <v>3.38</v>
       </c>
       <c r="P28">
-        <v>1.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA28">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-10 18:30:00</t>
+          <t>2026-08-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.73</v>
+        <v>4.41</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P29">
-        <v>4.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB29">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-10 19:30:00</t>
+          <t>2026-08-10 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-10 21:00:00</t>
+          <t>2026-08-10 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,156 +5804,482 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>2.01</v>
+      </c>
+      <c r="O34">
+        <v>2.91</v>
+      </c>
+      <c r="P34">
+        <v>4.2</v>
+      </c>
+      <c r="Q34">
+        <v>2.72</v>
+      </c>
+      <c r="R34">
+        <v>1.91</v>
+      </c>
+      <c r="S34">
+        <v>1.68</v>
+      </c>
+      <c r="T34">
+        <v>2.18</v>
+      </c>
+      <c r="U34">
+        <v>3.7</v>
+      </c>
+      <c r="V34">
+        <v>1.2</v>
+      </c>
+      <c r="W34">
+        <v>1.04</v>
+      </c>
+      <c r="X34">
+        <v>1.08</v>
+      </c>
+      <c r="Y34">
+        <v>1.68</v>
+      </c>
+      <c r="Z34">
+        <v>2.14</v>
+      </c>
+      <c r="AA34">
+        <v>2.59</v>
+      </c>
+      <c r="AB34">
+        <v>1.39</v>
+      </c>
+      <c r="AC34">
+        <v>5.67</v>
+      </c>
+      <c r="AD34">
+        <v>1.12</v>
+      </c>
+      <c r="AE34">
+        <v>1.03</v>
+      </c>
+      <c r="AF34">
+        <v>2.25</v>
+      </c>
+      <c r="AG34">
+        <v>1.54</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.31</v>
+      </c>
+      <c r="AK34">
+        <v>1.73</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>2.17</v>
+      </c>
+      <c r="O35">
+        <v>3.3</v>
+      </c>
+      <c r="P35">
+        <v>2.89</v>
+      </c>
+      <c r="Q35">
+        <v>2.88</v>
+      </c>
+      <c r="R35">
+        <v>1.98</v>
+      </c>
+      <c r="S35">
+        <v>1.4</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>2.85</v>
+      </c>
+      <c r="V35">
+        <v>1.36</v>
+      </c>
+      <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.3</v>
+      </c>
+      <c r="Z35">
+        <v>3.1</v>
+      </c>
+      <c r="AA35">
+        <v>2.05</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
+        <v>3.35</v>
+      </c>
+      <c r="AD35">
+        <v>1.28</v>
+      </c>
+      <c r="AE35">
+        <v>1.07</v>
+      </c>
+      <c r="AF35">
+        <v>1.78</v>
+      </c>
+      <c r="AG35">
+        <v>1.95</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.33</v>
+      </c>
+      <c r="AK35">
+        <v>1.53</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Deportivo Cuenca</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N34">
+      <c r="N36">
         <v>1.62</v>
       </c>
-      <c r="O34">
+      <c r="O36">
         <v>3.49</v>
       </c>
-      <c r="P34">
+      <c r="P36">
         <v>6.02</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
+      <c r="Q36">
+        <v>2.15</v>
+      </c>
+      <c r="R36">
+        <v>2</v>
+      </c>
+      <c r="S36">
+        <v>1.49</v>
+      </c>
+      <c r="T36">
+        <v>2.45</v>
+      </c>
+      <c r="U36">
+        <v>3.3</v>
+      </c>
+      <c r="V36">
+        <v>1.29</v>
+      </c>
+      <c r="W36">
+        <v>1.05</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.4</v>
+      </c>
+      <c r="Z36">
+        <v>2.6</v>
+      </c>
+      <c r="AA36">
+        <v>2.44</v>
+      </c>
+      <c r="AB36">
+        <v>1.53</v>
+      </c>
+      <c r="AC36">
+        <v>3.8</v>
+      </c>
+      <c r="AD36">
+        <v>1.15</v>
+      </c>
+      <c r="AE36">
+        <v>1.01</v>
+      </c>
+      <c r="AF36">
+        <v>2.15</v>
+      </c>
+      <c r="AG36">
+        <v>1.62</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.1</v>
+      </c>
+      <c r="AK36">
+        <v>2.14</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>2026-08-10 21:00:00</t>
         </is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q3">
         <v>2.08</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q17">
         <v>1.84</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="P20">
-        <v>2.77</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC20">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O21">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
@@ -3910,13 +3910,13 @@
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
         <v>2.84</v>
       </c>
       <c r="U22">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V22">
         <v>1.44</v>
@@ -3928,19 +3928,19 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD22">
         <v>1.36</v>
@@ -3949,7 +3949,7 @@
         <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
         <v>1.93</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q32">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
-        <v>3.76</v>
+        <v>5.35</v>
       </c>
       <c r="P13">
-        <v>1.88</v>
+        <v>8.1</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="R13">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>6.05</v>
       </c>
       <c r="AA13">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AC13">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="AD13">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE13">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.32</v>
+        <v>3.71</v>
       </c>
       <c r="O14">
-        <v>5.35</v>
+        <v>3.76</v>
       </c>
       <c r="P14">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q14">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="S14">
+        <v>1.22</v>
+      </c>
+      <c r="T14">
+        <v>3.34</v>
+      </c>
+      <c r="U14">
+        <v>2.25</v>
+      </c>
+      <c r="V14">
+        <v>1.57</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>1.13</v>
+      </c>
+      <c r="Z14">
+        <v>4.6</v>
+      </c>
+      <c r="AA14">
+        <v>1.5</v>
+      </c>
+      <c r="AB14">
+        <v>2.4</v>
+      </c>
+      <c r="AC14">
+        <v>2.33</v>
+      </c>
+      <c r="AD14">
+        <v>1.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.19</v>
+      </c>
+      <c r="AF14">
+        <v>1.5</v>
+      </c>
+      <c r="AG14">
+        <v>2.42</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.18</v>
+      </c>
+      <c r="AK14">
         <v>1.24</v>
-      </c>
-      <c r="T14">
-        <v>3.5</v>
-      </c>
-      <c r="U14">
-        <v>1.91</v>
-      </c>
-      <c r="V14">
-        <v>1.8</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.1</v>
-      </c>
-      <c r="Z14">
-        <v>6.05</v>
-      </c>
-      <c r="AA14">
-        <v>1.34</v>
-      </c>
-      <c r="AB14">
-        <v>3</v>
-      </c>
-      <c r="AC14">
-        <v>1.98</v>
-      </c>
-      <c r="AD14">
-        <v>1.83</v>
-      </c>
-      <c r="AE14">
-        <v>1.32</v>
-      </c>
-      <c r="AF14">
-        <v>1.6</v>
-      </c>
-      <c r="AG14">
-        <v>2.11</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.1</v>
-      </c>
-      <c r="AK14">
-        <v>3.3</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -644,7 +644,7 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R2">
         <v>2.15</v>
@@ -653,10 +653,10 @@
         <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -665,7 +665,7 @@
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.28</v>
@@ -674,10 +674,10 @@
         <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC2">
         <v>3.28</v>
@@ -686,13 +686,13 @@
         <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK3">
         <v>2</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O4">
         <v>3.4</v>
@@ -976,10 +976,10 @@
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -1000,22 +1000,22 @@
         <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB4">
         <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG4">
         <v>2.2</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
         <v>1.75</v>
@@ -1124,52 +1124,52 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="Q5">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R5">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="S5">
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
         <v>1.05</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
         <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AB5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AD5">
         <v>1.18</v>
@@ -1178,10 +1178,10 @@
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R7">
         <v>2.7</v>
@@ -1495,19 +1495,19 @@
         <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD7">
         <v>1.57</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R8">
         <v>1.93</v>
@@ -1655,7 +1655,7 @@
         <v>2.29</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AC8">
         <v>4.2</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
         <v>1.37</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
         <v>1.46</v>
@@ -1806,22 +1806,22 @@
         <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="AA9">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
         <v>2</v>
       </c>
       <c r="AC9">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
         <v>1.36</v>
@@ -1830,10 +1830,10 @@
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
         <v>3.05</v>
@@ -1954,7 +1954,7 @@
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
         <v>2.8</v>
@@ -1969,19 +1969,19 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
         <v>3.51</v>
@@ -1990,7 +1990,7 @@
         <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,16 +2111,16 @@
         <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U11">
         <v>2.59</v>
@@ -2135,25 +2135,25 @@
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
         <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
         <v>1.62</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -2292,25 +2292,25 @@
         <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
         <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD12">
         <v>1.32</v>
@@ -2322,7 +2322,7 @@
         <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="O13">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="P13">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R13">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
         <v>1.91</v>
@@ -2461,28 +2461,28 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>6.05</v>
+        <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC13">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD13">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE13">
         <v>1.32</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
         <v>2.11</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
         <v>3.3</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="O14">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2615,34 +2615,34 @@
         <v>2.25</v>
       </c>
       <c r="V14">
+        <v>1.58</v>
+      </c>
+      <c r="W14">
+        <v>1.13</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
+        <v>1.14</v>
+      </c>
+      <c r="Z14">
+        <v>5</v>
+      </c>
+      <c r="AA14">
+        <v>1.55</v>
+      </c>
+      <c r="AB14">
+        <v>2.32</v>
+      </c>
+      <c r="AC14">
+        <v>2.37</v>
+      </c>
+      <c r="AD14">
         <v>1.57</v>
       </c>
-      <c r="W14">
-        <v>1.11</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.13</v>
-      </c>
-      <c r="Z14">
-        <v>4.6</v>
-      </c>
-      <c r="AA14">
-        <v>1.5</v>
-      </c>
-      <c r="AB14">
-        <v>2.4</v>
-      </c>
-      <c r="AC14">
-        <v>2.33</v>
-      </c>
-      <c r="AD14">
-        <v>1.5</v>
-      </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
         <v>1.5</v>
@@ -2664,7 +2664,7 @@
         <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
         <v>3.6</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="R15">
         <v>2.4</v>
@@ -2772,34 +2772,34 @@
         <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U15">
         <v>2.15</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
         <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -2808,10 +2808,10 @@
         <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG15">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AK15">
         <v>1.44</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="O16">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q16">
         <v>2.93</v>
@@ -2956,25 +2956,25 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB16">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC16">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD16">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF16">
         <v>1.33</v>
       </c>
       <c r="AG16">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O18">
         <v>3</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
         <v>1.95</v>
@@ -3264,37 +3264,37 @@
         <v>2.35</v>
       </c>
       <c r="U18">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="V18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
         <v>1.01</v>
       </c>
       <c r="X18">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AA18">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AB18">
         <v>1.44</v>
       </c>
       <c r="AC18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD18">
         <v>1.12</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
         <v>2.25</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="O20">
-        <v>3.43</v>
+        <v>3.78</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q21">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="R21">
         <v>2.4</v>
@@ -3750,10 +3750,10 @@
         <v>1.19</v>
       </c>
       <c r="T21">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="U21">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
         <v>1.7</v>
@@ -3765,22 +3765,22 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
         <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD21">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE21">
         <v>1.28</v>
@@ -3789,7 +3789,7 @@
         <v>1.39</v>
       </c>
       <c r="AG21">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.22</v>
@@ -3934,10 +3934,10 @@
         <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC22">
         <v>2.69</v>
@@ -3949,10 +3949,10 @@
         <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>2.3</v>
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.44</v>
+        <v>3.65</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P25">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q25">
-        <v>5.34</v>
+        <v>4.33</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA25">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC25">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="AD25">
+        <v>1.3</v>
+      </c>
+      <c r="AE25">
+        <v>1.07</v>
+      </c>
+      <c r="AF25">
+        <v>1.71</v>
+      </c>
+      <c r="AG25">
+        <v>2.05</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.83</v>
+      </c>
+      <c r="AK25">
         <v>1.25</v>
-      </c>
-      <c r="AE25">
-        <v>1.05</v>
-      </c>
-      <c r="AF25">
-        <v>1.86</v>
-      </c>
-      <c r="AG25">
-        <v>1.84</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>2.01</v>
-      </c>
-      <c r="AK25">
-        <v>1.17</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="O26">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q26">
         <v>3.2</v>
@@ -4565,46 +4565,46 @@
         <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U26">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="V26">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
         <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA26">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC26">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD26">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="O27">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="Q27">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
         <v>2.88</v>
@@ -4728,13 +4728,13 @@
         <v>1.1</v>
       </c>
       <c r="T27">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="V27">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="W27">
         <v>1.36</v>
@@ -4743,47 +4743,47 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA27">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AB27">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AC27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD27">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AE27">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AF27">
+        <v>1.16</v>
+      </c>
+      <c r="AG27">
+        <v>4.5</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.22</v>
       </c>
-      <c r="AG27">
-        <v>3.9</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.19</v>
-      </c>
       <c r="AK27">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="O28">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
         <v>2.45</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -4894,43 +4894,43 @@
         <v>2.7</v>
       </c>
       <c r="U28">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
         <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AA28">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB28">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC28">
         <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
         <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG28">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.41</v>
+        <v>3.7</v>
       </c>
       <c r="O29">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
         <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.78</v>
+        <v>3.98</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
@@ -5229,7 +5229,7 @@
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
         <v>1.38</v>
@@ -5238,25 +5238,25 @@
         <v>2.95</v>
       </c>
       <c r="AA30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE30">
         <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG30">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P33">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="AB33">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O34">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P34">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S34">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="T34">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U34">
         <v>3.7</v>
@@ -5878,16 +5878,16 @@
         <v>1.2</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Z34">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AA34">
         <v>2.59</v>
@@ -5896,10 +5896,10 @@
         <v>1.39</v>
       </c>
       <c r="AC34">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="AD34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
         <v>1.73</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -6032,7 +6032,7 @@
         <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U35">
         <v>2.85</v>
@@ -6041,16 +6041,16 @@
         <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z35">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
         <v>2.05</v>
@@ -6065,13 +6065,13 @@
         <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
         <v>1.53</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O36">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>6.02</v>
+        <v>5.25</v>
       </c>
       <c r="Q36">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
         <v>2</v>
@@ -6210,10 +6210,10 @@
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z36">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA36">
         <v>2.44</v>
@@ -6222,16 +6222,16 @@
         <v>1.53</v>
       </c>
       <c r="AC36">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD36">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG36">
         <v>1.62</v>
@@ -6250,7 +6250,7 @@
         <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU36"/>
+  <dimension ref="A1:AU35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="O18">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>4.26</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="AB18">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC18">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>3.58</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>1.53</v>
+      </c>
+      <c r="AB21">
         <v>2.4</v>
       </c>
-      <c r="S21">
-        <v>1.19</v>
-      </c>
-      <c r="T21">
-        <v>3.85</v>
-      </c>
-      <c r="U21">
-        <v>2.05</v>
-      </c>
-      <c r="V21">
-        <v>1.7</v>
-      </c>
-      <c r="W21">
-        <v>1.15</v>
-      </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.08</v>
-      </c>
-      <c r="Z21">
-        <v>5.5</v>
-      </c>
-      <c r="AA21">
-        <v>1.47</v>
-      </c>
-      <c r="AB21">
-        <v>2.6</v>
-      </c>
       <c r="AC21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>5.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
+        <v>2.53</v>
+      </c>
+      <c r="R22">
+        <v>2.4</v>
+      </c>
+      <c r="S22">
+        <v>1.19</v>
+      </c>
+      <c r="T22">
+        <v>3.85</v>
+      </c>
+      <c r="U22">
         <v>2.05</v>
       </c>
-      <c r="R22">
-        <v>2.3</v>
-      </c>
-      <c r="S22">
-        <v>1.36</v>
-      </c>
-      <c r="T22">
-        <v>2.84</v>
-      </c>
-      <c r="U22">
-        <v>2.54</v>
-      </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AC22">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="AD22">
+        <v>1.66</v>
+      </c>
+      <c r="AE22">
+        <v>1.28</v>
+      </c>
+      <c r="AF22">
+        <v>1.39</v>
+      </c>
+      <c r="AG22">
+        <v>2.6</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.36</v>
       </c>
-      <c r="AE22">
-        <v>1.14</v>
-      </c>
-      <c r="AF22">
-        <v>1.75</v>
-      </c>
-      <c r="AG22">
-        <v>1.95</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.22</v>
-      </c>
       <c r="AK22">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-10 15:15:00</t>
+          <t>2026-08-10 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-10 15:30:00</t>
+          <t>2026-08-10 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.33</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P26">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q26">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="R26">
+        <v>2.09</v>
+      </c>
+      <c r="S26">
+        <v>1.33</v>
+      </c>
+      <c r="T26">
+        <v>3</v>
+      </c>
+      <c r="U26">
+        <v>2.69</v>
+      </c>
+      <c r="V26">
+        <v>1.4</v>
+      </c>
+      <c r="W26">
+        <v>1.08</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.25</v>
+      </c>
+      <c r="Z26">
+        <v>3.42</v>
+      </c>
+      <c r="AA26">
+        <v>1.85</v>
+      </c>
+      <c r="AB26">
+        <v>1.94</v>
+      </c>
+      <c r="AC26">
+        <v>3.11</v>
+      </c>
+      <c r="AD26">
+        <v>1.3</v>
+      </c>
+      <c r="AE26">
+        <v>1.07</v>
+      </c>
+      <c r="AF26">
+        <v>1.71</v>
+      </c>
+      <c r="AG26">
         <v>2.05</v>
       </c>
-      <c r="S26">
-        <v>1.4</v>
-      </c>
-      <c r="T26">
-        <v>2.63</v>
-      </c>
-      <c r="U26">
-        <v>2.9</v>
-      </c>
-      <c r="V26">
-        <v>1.33</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>1.36</v>
-      </c>
-      <c r="Z26">
-        <v>2.78</v>
-      </c>
-      <c r="AA26">
-        <v>2.1</v>
-      </c>
-      <c r="AB26">
-        <v>1.62</v>
-      </c>
-      <c r="AC26">
-        <v>3.68</v>
-      </c>
-      <c r="AD26">
-        <v>1.2</v>
-      </c>
-      <c r="AE26">
-        <v>1.04</v>
-      </c>
-      <c r="AF26">
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.83</v>
       </c>
-      <c r="AG26">
-        <v>1.83</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.3</v>
-      </c>
       <c r="AK26">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-10 16:00:00</t>
+          <t>2026-08-10 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
       <c r="Q27">
+        <v>3.2</v>
+      </c>
+      <c r="R27">
+        <v>2.05</v>
+      </c>
+      <c r="S27">
+        <v>1.4</v>
+      </c>
+      <c r="T27">
         <v>2.63</v>
       </c>
-      <c r="R27">
-        <v>2.88</v>
-      </c>
-      <c r="S27">
-        <v>1.1</v>
-      </c>
-      <c r="T27">
-        <v>6</v>
-      </c>
       <c r="U27">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
-        <v>2.21</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.04</v>
+      </c>
+      <c r="Y27">
         <v>1.36</v>
       </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
-      <c r="Y27">
+      <c r="Z27">
+        <v>2.78</v>
+      </c>
+      <c r="AA27">
+        <v>2.1</v>
+      </c>
+      <c r="AB27">
+        <v>1.62</v>
+      </c>
+      <c r="AC27">
+        <v>3.68</v>
+      </c>
+      <c r="AD27">
+        <v>1.2</v>
+      </c>
+      <c r="AE27">
         <v>1.04</v>
       </c>
-      <c r="Z27">
-        <v>12</v>
-      </c>
-      <c r="AA27">
-        <v>1.16</v>
-      </c>
-      <c r="AB27">
-        <v>4.7</v>
-      </c>
-      <c r="AC27">
-        <v>1.44</v>
-      </c>
-      <c r="AD27">
-        <v>2.6</v>
-      </c>
-      <c r="AE27">
-        <v>1.76</v>
-      </c>
       <c r="AF27">
-        <v>1.16</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:00</t>
+          <t>2026-08-10 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.86</v>
+        <v>2.52</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>2.11</v>
       </c>
       <c r="Q28">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="T28">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>2.21</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="AA28">
-        <v>2.17</v>
+        <v>1.16</v>
       </c>
       <c r="AB28">
-        <v>1.67</v>
+        <v>4.7</v>
       </c>
       <c r="AC28">
-        <v>3.8</v>
+        <v>1.44</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="AF28">
-        <v>1.9</v>
+        <v>1.16</v>
       </c>
       <c r="AG28">
-        <v>1.77</v>
+        <v>4.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.7</v>
+        <v>1.86</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
+        <v>4.33</v>
+      </c>
+      <c r="Q29">
+        <v>2.45</v>
+      </c>
+      <c r="R29">
+        <v>2.05</v>
+      </c>
+      <c r="S29">
+        <v>1.4</v>
+      </c>
+      <c r="T29">
+        <v>2.7</v>
+      </c>
+      <c r="U29">
+        <v>3</v>
+      </c>
+      <c r="V29">
+        <v>1.35</v>
+      </c>
+      <c r="W29">
+        <v>1.07</v>
+      </c>
+      <c r="X29">
+        <v>1.07</v>
+      </c>
+      <c r="Y29">
+        <v>1.36</v>
+      </c>
+      <c r="Z29">
+        <v>2.9</v>
+      </c>
+      <c r="AA29">
+        <v>2.17</v>
+      </c>
+      <c r="AB29">
+        <v>1.67</v>
+      </c>
+      <c r="AC29">
+        <v>3.8</v>
+      </c>
+      <c r="AD29">
+        <v>1.25</v>
+      </c>
+      <c r="AE29">
+        <v>1.04</v>
+      </c>
+      <c r="AF29">
         <v>1.9</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>1.9</v>
-      </c>
-      <c r="AB29">
-        <v>1.9</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-10 18:30:00</t>
+          <t>2026-08-10 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="O30">
         <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-10 19:30:00</t>
+          <t>2026-08-10 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,81 +5362,81 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="Q31">
-        <v>3.72</v>
+        <v>2.2</v>
       </c>
       <c r="R31">
+        <v>2.03</v>
+      </c>
+      <c r="S31">
+        <v>1.44</v>
+      </c>
+      <c r="T31">
+        <v>2.54</v>
+      </c>
+      <c r="U31">
+        <v>2.95</v>
+      </c>
+      <c r="V31">
+        <v>1.35</v>
+      </c>
+      <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>1.38</v>
+      </c>
+      <c r="Z31">
+        <v>2.95</v>
+      </c>
+      <c r="AA31">
+        <v>2.15</v>
+      </c>
+      <c r="AB31">
+        <v>1.67</v>
+      </c>
+      <c r="AC31">
+        <v>4.1</v>
+      </c>
+      <c r="AD31">
+        <v>1.2</v>
+      </c>
+      <c r="AE31">
+        <v>1.04</v>
+      </c>
+      <c r="AF31">
+        <v>2</v>
+      </c>
+      <c r="AG31">
+        <v>1.7</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.14</v>
+      </c>
+      <c r="AK31">
         <v>2.1</v>
       </c>
-      <c r="S31">
-        <v>1.4</v>
-      </c>
-      <c r="T31">
-        <v>2.65</v>
-      </c>
-      <c r="U31">
-        <v>2.81</v>
-      </c>
-      <c r="V31">
-        <v>1.4</v>
-      </c>
-      <c r="W31">
-        <v>1.06</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.3</v>
-      </c>
-      <c r="Z31">
-        <v>3.25</v>
-      </c>
-      <c r="AA31">
-        <v>1.95</v>
-      </c>
-      <c r="AB31">
-        <v>1.78</v>
-      </c>
-      <c r="AC31">
-        <v>3.28</v>
-      </c>
-      <c r="AD31">
-        <v>1.25</v>
-      </c>
-      <c r="AE31">
-        <v>1.06</v>
-      </c>
-      <c r="AF31">
-        <v>1.72</v>
-      </c>
-      <c r="AG31">
-        <v>1.96</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.57</v>
-      </c>
-      <c r="AK31">
-        <v>1.36</v>
-      </c>
       <c r="AL31">
         <v>0</v>
       </c>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>5.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="R32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK32">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="O33">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.26</v>
+        <v>5.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA33">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="O34">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="S34">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.15</v>
+        <v>2.82</v>
       </c>
       <c r="U34">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="V34">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="Z34">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="AD34">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-10 20:00:00</t>
+          <t>2026-08-10 21:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.06</v>
+        <v>5.25</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T35">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="U35">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W35">
         <v>1.05</v>
@@ -6047,31 +6047,31 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC35">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6117,169 +6117,6 @@
         <v>0</v>
       </c>
       <c r="AU35" t="inlineStr">
-        <is>
-          <t>2026-08-10 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N36">
-        <v>1.6</v>
-      </c>
-      <c r="O36">
-        <v>3.4</v>
-      </c>
-      <c r="P36">
-        <v>5.25</v>
-      </c>
-      <c r="Q36">
-        <v>2.2</v>
-      </c>
-      <c r="R36">
-        <v>2</v>
-      </c>
-      <c r="S36">
-        <v>1.49</v>
-      </c>
-      <c r="T36">
-        <v>2.45</v>
-      </c>
-      <c r="U36">
-        <v>3.3</v>
-      </c>
-      <c r="V36">
-        <v>1.29</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.41</v>
-      </c>
-      <c r="Z36">
-        <v>2.8</v>
-      </c>
-      <c r="AA36">
-        <v>2.44</v>
-      </c>
-      <c r="AB36">
-        <v>1.53</v>
-      </c>
-      <c r="AC36">
-        <v>4.3</v>
-      </c>
-      <c r="AD36">
-        <v>1.18</v>
-      </c>
-      <c r="AE36">
-        <v>1.05</v>
-      </c>
-      <c r="AF36">
-        <v>2.12</v>
-      </c>
-      <c r="AG36">
-        <v>1.62</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.1</v>
-      </c>
-      <c r="AK36">
-        <v>2.18</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>-1</v>
-      </c>
-      <c r="AN36">
-        <v>-1</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>-1</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
         <is>
           <t>2026-08-10 21:00:00</t>
         </is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -650,22 +650,22 @@
         <v>2.15</v>
       </c>
       <c r="S2">
+        <v>1.37</v>
+      </c>
+      <c r="T2">
+        <v>2.89</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
         <v>1.36</v>
       </c>
-      <c r="T2">
-        <v>2.88</v>
-      </c>
-      <c r="U2">
-        <v>2.97</v>
-      </c>
-      <c r="V2">
-        <v>1.4</v>
-      </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.28</v>
@@ -692,7 +692,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4574,7 +4574,7 @@
         <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4589,22 +4589,22 @@
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
         <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
         <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>5.3</v>
       </c>
       <c r="Q32">
-        <v>3.72</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
+        <v>1.84</v>
+      </c>
+      <c r="AC32">
+        <v>2.92</v>
+      </c>
+      <c r="AD32">
+        <v>1.31</v>
+      </c>
+      <c r="AE32">
+        <v>1.08</v>
+      </c>
+      <c r="AF32">
+        <v>1.86</v>
+      </c>
+      <c r="AG32">
         <v>1.78</v>
       </c>
-      <c r="AC32">
-        <v>3.28</v>
-      </c>
-      <c r="AD32">
-        <v>1.25</v>
-      </c>
-      <c r="AE32">
-        <v>1.06</v>
-      </c>
-      <c r="AF32">
-        <v>1.72</v>
-      </c>
-      <c r="AG32">
-        <v>1.96</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>5.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AG33">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK33">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.18</v>
@@ -846,13 +846,13 @@
         <v>2.55</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
         <v>2.05</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
         <v>2</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
         <v>3.4</v>
@@ -1012,7 +1012,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.61</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
         <v>1.75</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
+        <v>3.3</v>
+      </c>
+      <c r="P5">
         <v>3.5</v>
       </c>
-      <c r="P5">
-        <v>3.74</v>
-      </c>
       <c r="Q5">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R5">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB5">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AC5">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1459,25 +1459,25 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V7">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1486,28 +1486,28 @@
         <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AC7">
         <v>2.32</v>
       </c>
       <c r="AD7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AG7">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
         <v>4.05</v>
@@ -1670,7 +1670,7 @@
         <v>1.93</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O9">
         <v>3.25</v>
       </c>
       <c r="P9">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
         <v>2.17</v>
@@ -1794,28 +1794,28 @@
         <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
         <v>2</v>
@@ -1824,16 +1824,16 @@
         <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.67</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
         <v>1.24</v>
@@ -1975,7 +1975,7 @@
         <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA10">
         <v>1.98</v>
@@ -2012,7 +2012,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
@@ -2144,7 +2144,7 @@
         <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC11">
         <v>2.98</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
         <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R12">
         <v>2.29</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O13">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
         <v>1.67</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
         <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB13">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC13">
         <v>1.94</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P14">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.22</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V14">
         <v>1.58</v>
@@ -2621,7 +2621,7 @@
         <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
@@ -2630,10 +2630,10 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC14">
         <v>2.37</v>
@@ -2642,13 +2642,13 @@
         <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
         <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q15">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2799,19 +2799,19 @@
         <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AD15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG15">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q16">
         <v>2.93</v>
@@ -2944,13 +2944,13 @@
         <v>1.83</v>
       </c>
       <c r="W16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -2959,7 +2959,7 @@
         <v>1.3</v>
       </c>
       <c r="AB16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC16">
         <v>1.83</v>
@@ -2974,7 +2974,7 @@
         <v>1.33</v>
       </c>
       <c r="AG16">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AA19">
         <v>2.43</v>
@@ -3451,10 +3451,10 @@
         <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AD19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
         <v>1.02</v>
@@ -3479,7 +3479,7 @@
         <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -3608,25 +3608,25 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="O21">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="P22">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q22">
         <v>2.53</v>
@@ -3916,7 +3916,7 @@
         <v>3.85</v>
       </c>
       <c r="U22">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V22">
         <v>1.7</v>
@@ -3934,10 +3934,10 @@
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AB22">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2.05</v>
@@ -3946,7 +3946,7 @@
         <v>1.66</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
@@ -3968,7 +3968,7 @@
         <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>5.14</v>
       </c>
       <c r="Q23">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
         <v>2.84</v>
       </c>
       <c r="U23">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="P27">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4746,7 +4746,7 @@
         <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="Q28">
         <v>2.63</v>
@@ -4891,7 +4891,7 @@
         <v>1.1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="U28">
         <v>1.58</v>
@@ -4909,7 +4909,7 @@
         <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA28">
         <v>1.16</v>
@@ -4924,7 +4924,7 @@
         <v>2.6</v>
       </c>
       <c r="AE28">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AF28">
         <v>1.16</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O29">
         <v>3.3</v>
@@ -5075,7 +5075,7 @@
         <v>2.9</v>
       </c>
       <c r="AA29">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB29">
         <v>1.67</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P30">
         <v>1.9</v>
@@ -5365,10 +5365,10 @@
         <v>1.67</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5389,7 +5389,7 @@
         <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5419,7 +5419,7 @@
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>5.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>3.72</v>
       </c>
       <c r="R32">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
         <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK32">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.8</v>
+        <v>1.54</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>3.72</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AB33">
+        <v>1.84</v>
+      </c>
+      <c r="AC33">
+        <v>2.92</v>
+      </c>
+      <c r="AD33">
+        <v>1.31</v>
+      </c>
+      <c r="AE33">
+        <v>1.08</v>
+      </c>
+      <c r="AF33">
+        <v>1.86</v>
+      </c>
+      <c r="AG33">
         <v>1.78</v>
       </c>
-      <c r="AC33">
-        <v>3.28</v>
-      </c>
-      <c r="AD33">
-        <v>1.25</v>
-      </c>
-      <c r="AE33">
-        <v>1.06</v>
-      </c>
-      <c r="AF33">
-        <v>1.72</v>
-      </c>
-      <c r="AG33">
-        <v>1.96</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="P34">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5878,7 +5878,7 @@
         <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.04</v>
@@ -5902,7 +5902,7 @@
         <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
@@ -6014,55 +6014,55 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T35">
         <v>2.45</v>
       </c>
       <c r="U35">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="V35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W35">
+        <v>1.02</v>
+      </c>
+      <c r="X35">
         <v>1.05</v>
       </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
       <c r="Y35">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z35">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AA35">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AB35">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC35">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE35">
         <v>1.05</v>
@@ -6071,7 +6071,7 @@
         <v>2.12</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -650,25 +650,25 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
         <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
         <v>3.05</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1145,43 +1145,43 @@
         <v>2.62</v>
       </c>
       <c r="U5">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="V5">
         <v>1.33</v>
       </c>
       <c r="W5">
+        <v>1.03</v>
+      </c>
+      <c r="X5">
         <v>1.06</v>
-      </c>
-      <c r="X5">
-        <v>1.08</v>
       </c>
       <c r="Y5">
         <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA5">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC5">
         <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>3.25</v>
@@ -1794,7 +1794,7 @@
         <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="U9">
         <v>2.63</v>
@@ -1809,13 +1809,13 @@
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
         <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
         <v>2</v>
@@ -1824,7 +1824,7 @@
         <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.13</v>
+        <v>3.58</v>
       </c>
       <c r="O21">
         <v>3.75</v>
       </c>
       <c r="P21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="O22">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="P22">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="Q22">
         <v>2.53</v>
@@ -3919,7 +3919,7 @@
         <v>2.09</v>
       </c>
       <c r="V22">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3928,13 +3928,13 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AB22">
         <v>2.7</v>
@@ -3946,7 +3946,7 @@
         <v>1.66</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
@@ -4088,7 +4088,7 @@
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.22</v>
@@ -4553,10 +4553,10 @@
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="Q26">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="R26">
         <v>2.15</v>
@@ -4571,7 +4571,7 @@
         <v>2.69</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.83</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="O29">
         <v>3.3</v>
@@ -5051,10 +5051,10 @@
         <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U29">
         <v>3</v>
@@ -5075,7 +5075,7 @@
         <v>2.9</v>
       </c>
       <c r="AA29">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
         <v>1.67</v>
@@ -5090,7 +5090,7 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
         <v>1.77</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
         <v>1.89</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>1.54</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>3.72</v>
+        <v>2.08</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="U32">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AB32">
         <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.54</v>
+        <v>2.8</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>3.72</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z33">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
         <v>1.84</v>
       </c>
       <c r="AC33">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AD33">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AG33">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK33">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="P19">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
         <v>2.4</v>
@@ -3427,25 +3427,25 @@
         <v>2.35</v>
       </c>
       <c r="U19">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z19">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA19">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AB19">
         <v>1.44</v>
@@ -3454,10 +3454,10 @@
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
         <v>2.25</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.91</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="O27">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P27">
         <v>2.55</v>
@@ -4728,7 +4728,7 @@
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U27">
         <v>2.9</v>
@@ -4746,13 +4746,13 @@
         <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
         <v>3.68</v>
@@ -4761,7 +4761,7 @@
         <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
         <v>1.83</v>
@@ -5365,10 +5365,10 @@
         <v>1.67</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>4.87</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5383,13 +5383,13 @@
         <v>2.54</v>
       </c>
       <c r="U31">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="V31">
         <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5407,19 +5407,19 @@
         <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P35">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R35">
         <v>2</v>
@@ -6035,28 +6035,28 @@
         <v>2.45</v>
       </c>
       <c r="U35">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="V35">
         <v>1.3</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
         <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z35">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AA35">
         <v>2.5</v>
       </c>
       <c r="AB35">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC35">
         <v>4.5</v>
@@ -6068,7 +6068,7 @@
         <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AG35">
         <v>1.53</v>
@@ -6087,7 +6087,7 @@
         <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -644,28 +644,28 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="U2">
         <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
@@ -689,10 +689,10 @@
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
         <v>2.45</v>
@@ -991,10 +991,10 @@
         <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
         <v>3.9</v>
@@ -1003,7 +1003,7 @@
         <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
@@ -1012,7 +1012,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
         <v>1.61</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
         <v>1.75</v>
@@ -1127,10 +1127,10 @@
         <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1160,10 +1160,10 @@
         <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AB5">
         <v>1.68</v>
@@ -1172,16 +1172,16 @@
         <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>1.48</v>
@@ -1670,7 +1670,7 @@
         <v>1.93</v>
       </c>
       <c r="AG8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="AK8">
         <v>1.37</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O9">
         <v>3.25</v>
@@ -1785,10 +1785,10 @@
         <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
         <v>1.32</v>
@@ -1797,34 +1797,34 @@
         <v>2.96</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.09</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
         <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC9">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
         <v>3.2</v>
@@ -1954,13 +1954,13 @@
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
         <v>1.37</v>
@@ -2012,7 +2012,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U11">
         <v>2.59</v>
@@ -2132,7 +2132,7 @@
         <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
@@ -2144,22 +2144,22 @@
         <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AD11">
         <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R15">
         <v>2.38</v>
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="U15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
         <v>1.64</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA15">
         <v>1.5</v>
@@ -2799,19 +2799,19 @@
         <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AD15">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3898,10 +3898,10 @@
         <v>2.11</v>
       </c>
       <c r="O22">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="Q22">
         <v>2.53</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC22">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD22">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>5.14</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R23">
         <v>2.3</v>
@@ -4106,7 +4106,7 @@
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P26">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="Q26">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4577,10 +4577,10 @@
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
         <v>3.42</v>
@@ -4592,16 +4592,16 @@
         <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="AD26">
         <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5051,13 +5051,13 @@
         <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V29">
         <v>1.35</v>
@@ -5069,31 +5069,31 @@
         <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
         <v>1.89</v>
@@ -5365,10 +5365,10 @@
         <v>1.67</v>
       </c>
       <c r="O31">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5389,7 +5389,7 @@
         <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5525,22 +5525,22 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
         <v>5</v>
       </c>
       <c r="Q32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
         <v>2.83</v>
@@ -5555,34 +5555,34 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB32">
         <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
         <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AG32">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q33">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W33">
         <v>1.06</v>
@@ -5721,31 +5721,31 @@
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB33">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
         <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         <v>2.17</v>
       </c>
       <c r="O34">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5878,13 +5878,13 @@
         <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
         <v>2.97</v>
@@ -5893,7 +5893,7 @@
         <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
         <v>3.35</v>
@@ -5902,13 +5902,13 @@
         <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
         <v>1.53</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -807,7 +807,7 @@
         <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
         <v>2.26</v>
@@ -819,10 +819,10 @@
         <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.12</v>
@@ -837,19 +837,19 @@
         <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
         <v>2.55</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
         <v>1.65</v>
@@ -871,7 +871,7 @@
         <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
         <v>2.38</v>
@@ -1471,13 +1471,13 @@
         <v>3.08</v>
       </c>
       <c r="U7">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1486,19 +1486,19 @@
         <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AC7">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AD7">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE7">
         <v>1.19</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="Q12">
         <v>2.83</v>
@@ -2280,7 +2280,7 @@
         <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -2304,22 +2304,22 @@
         <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC12">
         <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
         <v>2.17</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="Q13">
         <v>1.67</v>
@@ -2443,10 +2443,10 @@
         <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="U13">
         <v>1.91</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
         <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC13">
         <v>1.94</v>
@@ -2501,7 +2501,7 @@
         <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q14">
         <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2624,19 +2624,19 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA14">
         <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AD14">
         <v>1.57</v>
@@ -2645,7 +2645,7 @@
         <v>1.19</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG14">
         <v>2.39</v>
@@ -2920,7 +2920,7 @@
         <v>2.52</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P16">
         <v>1.97</v>
@@ -2950,19 +2950,19 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z16">
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AB16">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD16">
         <v>1.91</v>
@@ -2971,7 +2971,7 @@
         <v>1.35</v>
       </c>
       <c r="AF16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG16">
         <v>3</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3095,10 +3095,10 @@
         <v>2.63</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -3107,10 +3107,10 @@
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.12</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
         <v>2.4</v>
@@ -3427,19 +3427,19 @@
         <v>2.35</v>
       </c>
       <c r="U19">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V19">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y19">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z19">
         <v>2.4</v>
@@ -3448,7 +3448,7 @@
         <v>2.5</v>
       </c>
       <c r="AB19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -3584,10 +3584,10 @@
         <v>2.75</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U20">
         <v>1.96</v>
@@ -3596,16 +3596,16 @@
         <v>1.65</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20">
         <v>1.41</v>
@@ -3617,7 +3617,7 @@
         <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE20">
         <v>1.25</v>
@@ -4731,13 +4731,13 @@
         <v>2.47</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
         <v>1.04</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="S28">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T28">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="U28">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V28">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="W28">
         <v>1.36</v>
@@ -4909,10 +4909,10 @@
         <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA28">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AB28">
         <v>4.7</v>
@@ -4921,16 +4921,16 @@
         <v>1.44</v>
       </c>
       <c r="AD28">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AE28">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AF28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AG28">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>1.98</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
         <v>2.82</v>
@@ -6023,7 +6023,7 @@
         <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R35">
         <v>2</v>
@@ -6053,7 +6053,7 @@
         <v>2.6</v>
       </c>
       <c r="AA35">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AB35">
         <v>1.53</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1465,10 +1465,10 @@
         <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="U7">
         <v>2.25</v>
@@ -1477,37 +1477,37 @@
         <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
         <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="AC7">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD7">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE7">
         <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>2.29</v>
       </c>
       <c r="AB8">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AC8">
         <v>4.2</v>
@@ -1670,7 +1670,7 @@
         <v>1.93</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q10">
         <v>3.05</v>
@@ -1957,7 +1957,7 @@
         <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.77</v>
@@ -1990,7 +1990,7 @@
         <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2141,7 +2141,7 @@
         <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB11">
         <v>2</v>
@@ -2159,7 +2159,7 @@
         <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
         <v>3.45</v>
@@ -2274,7 +2274,7 @@
         <v>2.85</v>
       </c>
       <c r="Q12">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
         <v>2.29</v>
@@ -2310,10 +2310,10 @@
         <v>1.99</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
@@ -2434,7 +2434,7 @@
         <v>5.1</v>
       </c>
       <c r="P13">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
         <v>1.67</v>
@@ -2446,7 +2446,7 @@
         <v>1.18</v>
       </c>
       <c r="T13">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U13">
         <v>1.91</v>
@@ -2467,7 +2467,7 @@
         <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB13">
         <v>3.1</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O14">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
         <v>1.73</v>
@@ -2603,7 +2603,7 @@
         <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2615,7 +2615,7 @@
         <v>2.27</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2645,7 +2645,7 @@
         <v>1.19</v>
       </c>
       <c r="AF14">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
         <v>2.39</v>
@@ -2920,7 +2920,7 @@
         <v>2.52</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="P16">
         <v>1.97</v>
@@ -2950,19 +2950,19 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z16">
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AB16">
         <v>3.1</v>
       </c>
       <c r="AC16">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD16">
         <v>1.91</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.33</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -650,7 +650,7 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
         <v>2.89</v>
@@ -665,16 +665,16 @@
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
         <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB2">
         <v>1.78</v>
@@ -683,7 +683,7 @@
         <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R3">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U3">
         <v>2.28</v>
@@ -828,10 +828,10 @@
         <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
         <v>3.9</v>
@@ -843,19 +843,19 @@
         <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK3">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
         <v>3.2</v>
@@ -991,7 +991,7 @@
         <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.19</v>
@@ -1000,7 +1000,7 @@
         <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB4">
         <v>2</v>
@@ -1009,7 +1009,7 @@
         <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
         <v>1.11</v>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
         <v>3.6</v>
@@ -1151,7 +1151,7 @@
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.06</v>
@@ -1172,7 +1172,7 @@
         <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>1.52</v>
+      </c>
+      <c r="R7">
+        <v>2.85</v>
+      </c>
+      <c r="S7">
+        <v>1.2</v>
+      </c>
+      <c r="T7">
+        <v>3.7</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
         <v>1.73</v>
       </c>
-      <c r="R7">
-        <v>2.38</v>
-      </c>
-      <c r="S7">
-        <v>1.21</v>
-      </c>
-      <c r="T7">
-        <v>3.58</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
-      <c r="V7">
-        <v>1.57</v>
-      </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>5.65</v>
       </c>
       <c r="AA7">
         <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AC7">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK7">
-        <v>2.83</v>
+        <v>4.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q8">
-        <v>3.79</v>
+        <v>3.93</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S8">
         <v>1.48</v>
@@ -1661,7 +1661,7 @@
         <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AK8">
         <v>1.37</v>
@@ -1785,25 +1785,25 @@
         <v>2.05</v>
       </c>
       <c r="Q9">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="R9">
         <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,10 +1812,10 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
         <v>2.01</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O10">
         <v>3.2</v>
@@ -1957,7 +1957,7 @@
         <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U10">
         <v>2.77</v>
@@ -1978,7 +1978,7 @@
         <v>3.14</v>
       </c>
       <c r="AA10">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
         <v>1.78</v>
@@ -2153,13 +2153,13 @@
         <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2271,16 +2271,16 @@
         <v>3.45</v>
       </c>
       <c r="P12">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R12">
         <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -2304,10 +2304,10 @@
         <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
         <v>2.95</v>
@@ -2431,7 +2431,7 @@
         <v>1.3</v>
       </c>
       <c r="O13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>7.5</v>
@@ -2443,10 +2443,10 @@
         <v>2.75</v>
       </c>
       <c r="S13">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T13">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
         <v>1.91</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
         <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB13">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AC13">
         <v>1.94</v>
@@ -2501,7 +2501,7 @@
         <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>2.27</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2636,7 +2636,7 @@
         <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD14">
         <v>1.57</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="P15">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
         <v>3.14</v>
@@ -2772,7 +2772,7 @@
         <v>1.22</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U15">
         <v>2.2</v>
@@ -2787,19 +2787,19 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -3089,25 +3089,25 @@
         <v>5.91</v>
       </c>
       <c r="Q17">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3584,10 +3584,10 @@
         <v>2.75</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T20">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="U20">
         <v>1.96</v>
@@ -3596,28 +3596,28 @@
         <v>1.65</v>
       </c>
       <c r="W20">
+        <v>1.12</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
         <v>1.14</v>
       </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.09</v>
-      </c>
       <c r="Z20">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA20">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB20">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC20">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AD20">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE20">
         <v>1.25</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3919,7 +3919,7 @@
         <v>2.09</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3937,22 +3937,22 @@
         <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC22">
         <v>2.1</v>
       </c>
       <c r="AD22">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.7</v>
@@ -4076,25 +4076,25 @@
         <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="U23">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA23">
         <v>1.75</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
         <v>2.4</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
         <v>3.54</v>
       </c>
       <c r="P26">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4568,40 +4568,40 @@
         <v>3</v>
       </c>
       <c r="U26">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB26">
         <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>3.11</v>
+        <v>3.33</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
         <v>2.55</v>
@@ -4746,7 +4746,7 @@
         <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
@@ -4761,7 +4761,7 @@
         <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
         <v>1.83</v>
@@ -4912,7 +4912,7 @@
         <v>12</v>
       </c>
       <c r="AA28">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AB28">
         <v>4.7</v>
@@ -4921,10 +4921,10 @@
         <v>1.44</v>
       </c>
       <c r="AD28">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AE28">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF28">
         <v>1.2</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5057,7 +5057,7 @@
         <v>2.75</v>
       </c>
       <c r="U29">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
         <v>1.35</v>
@@ -5069,16 +5069,16 @@
         <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z29">
         <v>2.83</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB29">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5090,7 +5090,7 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
         <v>1.8</v>
@@ -5202,10 +5202,10 @@
         <v>3.95</v>
       </c>
       <c r="O30">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
       </c>
       <c r="R31">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S31">
         <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U31">
         <v>2.91</v>
@@ -5389,7 +5389,7 @@
         <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.05</v>
@@ -5419,7 +5419,7 @@
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>1.56</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -5537,7 +5537,7 @@
         <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
         <v>1.34</v>
@@ -5561,13 +5561,13 @@
         <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB32">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC32">
         <v>2.97</v>
@@ -5582,7 +5582,7 @@
         <v>1.82</v>
       </c>
       <c r="AG32">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,46 +5688,46 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="O33">
         <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="T33">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
         <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB33">
         <v>1.82</v>
@@ -5736,10 +5736,10 @@
         <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
         <v>1.68</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK33">
         <v>1.36</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O35">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
         <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T35">
         <v>2.45</v>
@@ -6038,13 +6038,13 @@
         <v>3.25</v>
       </c>
       <c r="V35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W35">
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.44</v>
@@ -6053,13 +6053,13 @@
         <v>2.6</v>
       </c>
       <c r="AA35">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AB35">
         <v>1.53</v>
       </c>
       <c r="AC35">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD35">
         <v>1.17</v>
@@ -6087,7 +6087,7 @@
         <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -653,7 +653,7 @@
         <v>1.39</v>
       </c>
       <c r="T2">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
         <v>2.75</v>
@@ -662,10 +662,10 @@
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.28</v>
@@ -674,7 +674,7 @@
         <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
         <v>1.78</v>
@@ -683,7 +683,7 @@
         <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
         <v>3.2</v>
@@ -997,22 +997,22 @@
         <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.61</v>
@@ -1127,10 +1127,10 @@
         <v>1.91</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1142,16 +1142,16 @@
         <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U5">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.06</v>
@@ -1160,22 +1160,22 @@
         <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AB5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
         <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
         <v>1.91</v>
@@ -1646,31 +1646,31 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AA8">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB8">
         <v>1.63</v>
       </c>
       <c r="AC8">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1794,7 +1794,7 @@
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U9">
         <v>2.63</v>
@@ -1806,19 +1806,19 @@
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
         <v>2.86</v>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
         <v>2.83</v>
@@ -2304,16 +2304,16 @@
         <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC12">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
@@ -2431,16 +2431,16 @@
         <v>1.3</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q13">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R13">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="S13">
         <v>1.23</v>
@@ -2467,10 +2467,10 @@
         <v>6.7</v>
       </c>
       <c r="AA13">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AB13">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC13">
         <v>1.94</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK13">
         <v>3.13</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P14">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
         <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S14">
         <v>1.22</v>
       </c>
       <c r="T14">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
         <v>2.27</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2627,10 +2627,10 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB14">
         <v>2.3</v>
@@ -3409,10 +3409,10 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="P19">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
         <v>2.4</v>
@@ -3433,7 +3433,7 @@
         <v>1.22</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.11</v>
@@ -3442,10 +3442,10 @@
         <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA19">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AB19">
         <v>1.43</v>
@@ -3454,7 +3454,7 @@
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK19">
         <v>1.91</v>
@@ -3738,7 +3738,7 @@
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P22">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="Q22">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="R22">
         <v>2.4</v>
@@ -3913,13 +3913,13 @@
         <v>1.19</v>
       </c>
       <c r="T22">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="U22">
         <v>2.09</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3928,7 +3928,7 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
@@ -3937,13 +3937,13 @@
         <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC22">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD22">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE22">
         <v>1.25</v>
@@ -3952,7 +3952,7 @@
         <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.23</v>
@@ -4131,7 +4131,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4550,13 +4550,13 @@
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
         <v>1.91</v>
       </c>
       <c r="Q26">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4571,7 +4571,7 @@
         <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
         <v>1.04</v>
@@ -4583,7 +4583,7 @@
         <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AA26">
         <v>1.92</v>
@@ -4601,7 +4601,7 @@
         <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -5042,7 +5042,7 @@
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>3.71</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5066,7 +5066,7 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
         <v>1.38</v>
@@ -5075,10 +5075,10 @@
         <v>2.83</v>
       </c>
       <c r="AA29">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5090,10 +5090,10 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5407,19 +5407,19 @@
         <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
         <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5866,7 +5866,7 @@
         <v>1.98</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
         <v>2.82</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
         <v>1.53</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -3409,13 +3409,13 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>2.78</v>
+        <v>3.06</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
         <v>1.95</v>
@@ -3433,7 +3433,7 @@
         <v>1.22</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X19">
         <v>1.11</v>
@@ -3445,16 +3445,16 @@
         <v>2.45</v>
       </c>
       <c r="AA19">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AB19">
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.91</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4734,7 +4734,7 @@
         <v>2.95</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4743,16 +4743,16 @@
         <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z27">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
         <v>3.68</v>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P30">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O31">
         <v>3.4</v>
@@ -5386,13 +5386,13 @@
         <v>2.91</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
         <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.38</v>
@@ -5410,13 +5410,13 @@
         <v>3.97</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG31">
         <v>1.7</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="O32">
         <v>3.7</v>
@@ -5534,16 +5534,16 @@
         <v>5</v>
       </c>
       <c r="Q32">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R32">
         <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="U32">
         <v>2.5</v>
@@ -5555,50 +5555,50 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA32">
         <v>1.82</v>
       </c>
       <c r="AB32">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
+        <v>1.1</v>
+      </c>
+      <c r="AF32">
+        <v>1.86</v>
+      </c>
+      <c r="AG32">
+        <v>1.78</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.08</v>
       </c>
-      <c r="AF32">
-        <v>1.82</v>
-      </c>
-      <c r="AG32">
-        <v>1.85</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.19</v>
-      </c>
       <c r="AK32">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="O33">
         <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q33">
         <v>3.64</v>
@@ -5727,16 +5727,16 @@
         <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
         <v>1.07</v>
@@ -5761,7 +5761,7 @@
         <v>1.53</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="U34">
         <v>2.85</v>
@@ -5878,37 +5878,37 @@
         <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>3.13</v>
+      </c>
+      <c r="AA34">
+        <v>2.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.73</v>
+      </c>
+      <c r="AC34">
+        <v>3.25</v>
+      </c>
+      <c r="AD34">
         <v>1.3</v>
       </c>
-      <c r="Z34">
-        <v>2.97</v>
-      </c>
-      <c r="AA34">
-        <v>2.05</v>
-      </c>
-      <c r="AB34">
-        <v>1.7</v>
-      </c>
-      <c r="AC34">
-        <v>3.35</v>
-      </c>
-      <c r="AD34">
-        <v>1.28</v>
-      </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6044,10 +6044,10 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z35">
         <v>2.6</v>
@@ -6056,7 +6056,7 @@
         <v>2.46</v>
       </c>
       <c r="AB35">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC35">
         <v>4.4</v>
@@ -6087,7 +6087,7 @@
         <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -5528,28 +5528,28 @@
         <v>1.57</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
         <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
         <v>1.08</v>
@@ -5564,25 +5564,25 @@
         <v>3.45</v>
       </c>
       <c r="AA32">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB32">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
         <v>1.1</v>
       </c>
       <c r="AF32">
+        <v>1.81</v>
+      </c>
+      <c r="AG32">
         <v>1.86</v>
-      </c>
-      <c r="AG32">
-        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5697,28 +5697,28 @@
         <v>2.13</v>
       </c>
       <c r="Q33">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
         <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V33">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
         <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.32</v>
@@ -5730,16 +5730,16 @@
         <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
         <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.68</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -647,10 +647,10 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>2.88</v>
@@ -659,13 +659,13 @@
         <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
         <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.28</v>
@@ -674,16 +674,16 @@
         <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
         <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,10 +807,10 @@
         <v>4.33</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
         <v>1.28</v>
@@ -819,7 +819,7 @@
         <v>3.14</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
         <v>1.48</v>
@@ -828,34 +828,34 @@
         <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
+        <v>1.64</v>
+      </c>
+      <c r="AB3">
+        <v>2.1</v>
+      </c>
+      <c r="AC3">
+        <v>2.63</v>
+      </c>
+      <c r="AD3">
+        <v>1.4</v>
+      </c>
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
         <v>1.67</v>
       </c>
-      <c r="AB3">
-        <v>2.15</v>
-      </c>
-      <c r="AC3">
-        <v>2.62</v>
-      </c>
-      <c r="AD3">
-        <v>1.38</v>
-      </c>
-      <c r="AE3">
-        <v>1.11</v>
-      </c>
-      <c r="AF3">
-        <v>1.66</v>
-      </c>
       <c r="AG3">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
         <v>3.2</v>
@@ -991,16 +991,16 @@
         <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
         <v>2.1</v>
@@ -1012,7 +1012,7 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
         <v>1.61</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1142,46 +1142,46 @@
         <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="V5">
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
         <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AB5">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
         <v>1.8</v>
@@ -1459,22 +1459,22 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R7">
         <v>2.85</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T7">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="W7">
         <v>1.17</v>
@@ -1486,25 +1486,25 @@
         <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AA7">
         <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AC7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AE7">
         <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AG7">
         <v>1.72</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK7">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1628,10 +1628,10 @@
         <v>2.09</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="U8">
         <v>3.32</v>
@@ -1646,22 +1646,22 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AA8">
         <v>2.27</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
         <v>4.15</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1686,7 +1686,7 @@
         <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,25 +1779,25 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
         <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V9">
         <v>1.44</v>
@@ -1806,28 +1806,28 @@
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
         <v>2.86</v>
       </c>
       <c r="AD9">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
         <v>3.2</v>
@@ -1948,16 +1948,16 @@
         <v>2.75</v>
       </c>
       <c r="Q10">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R10">
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="U10">
         <v>2.77</v>
@@ -1969,16 +1969,16 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
         <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB10">
         <v>1.78</v>
@@ -1990,7 +1990,7 @@
         <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2012,7 +2012,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
@@ -2141,10 +2141,10 @@
         <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC11">
         <v>2.97</v>
@@ -2153,13 +2153,13 @@
         <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,13 +2274,13 @@
         <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="R12">
         <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -2304,16 +2304,16 @@
         <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
         <v>1.96</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
@@ -2338,7 +2338,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
         <v>3.14</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA15">
         <v>1.5</v>
@@ -2799,7 +2799,7 @@
         <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -2808,7 +2808,7 @@
         <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG15">
         <v>2.69</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="O16">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
         <v>1.97</v>
@@ -2953,13 +2953,13 @@
         <v>1.08</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AA16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB16">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AC16">
         <v>1.83</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3738,7 +3738,7 @@
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3916,10 +3916,10 @@
         <v>3.88</v>
       </c>
       <c r="U22">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="V22">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3928,16 +3928,16 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AB22">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AC22">
         <v>2.09</v>
@@ -3946,13 +3946,13 @@
         <v>1.7</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF22">
         <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>1.7</v>
@@ -4067,34 +4067,34 @@
         <v>5.14</v>
       </c>
       <c r="Q23">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
         <v>1.75</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK23">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4580,16 +4580,16 @@
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC26">
         <v>3.33</v>
@@ -4598,7 +4598,7 @@
         <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.75</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="R28">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="S28">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T28">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="U28">
         <v>1.6</v>
@@ -4909,7 +4909,7 @@
         <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA28">
         <v>1.12</v>
@@ -4921,7 +4921,7 @@
         <v>1.44</v>
       </c>
       <c r="AD28">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AE28">
         <v>1.75</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AK28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O29">
         <v>3.3</v>
       </c>
       <c r="P29">
-        <v>3.71</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5054,7 +5054,7 @@
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U29">
         <v>3.1</v>
@@ -5066,7 +5066,7 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.38</v>
@@ -5084,16 +5084,16 @@
         <v>3.8</v>
       </c>
       <c r="AD29">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="O30">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -5413,7 +5413,7 @@
         <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
         <v>2</v>
@@ -5531,7 +5531,7 @@
         <v>3.75</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>2</v>
@@ -5576,7 +5576,7 @@
         <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.81</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q33">
         <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
         <v>2.9</v>
       </c>
       <c r="U33">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="V33">
         <v>1.35</v>
@@ -5724,25 +5724,25 @@
         <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA33">
         <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC33">
         <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
         <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
         <v>2.05</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AK33">
         <v>1.32</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O35">
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q35">
         <v>2.22</v>
@@ -6065,7 +6065,7 @@
         <v>1.17</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF35">
         <v>2.25</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O13">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
         <v>1.64</v>
@@ -2443,10 +2443,10 @@
         <v>2.76</v>
       </c>
       <c r="S13">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="U13">
         <v>1.91</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AC13">
         <v>1.94</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
         <v>3.13</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="O14">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q14">
         <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2615,7 +2615,7 @@
         <v>2.27</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2627,16 +2627,16 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA14">
         <v>1.54</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD14">
         <v>1.57</v>
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="O17">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>5.91</v>
+        <v>3.99</v>
       </c>
       <c r="Q17">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>3.5</v>
@@ -3104,40 +3104,40 @@
         <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
+        <v>1.15</v>
+      </c>
+      <c r="Z17">
+        <v>4.5</v>
+      </c>
+      <c r="AA17">
+        <v>1.55</v>
+      </c>
+      <c r="AB17">
+        <v>2.35</v>
+      </c>
+      <c r="AC17">
+        <v>2.45</v>
+      </c>
+      <c r="AD17">
+        <v>1.5</v>
+      </c>
+      <c r="AE17">
         <v>1.12</v>
-      </c>
-      <c r="Z17">
-        <v>4.8</v>
-      </c>
-      <c r="AA17">
-        <v>1.43</v>
-      </c>
-      <c r="AB17">
-        <v>2.48</v>
-      </c>
-      <c r="AC17">
-        <v>2.08</v>
-      </c>
-      <c r="AD17">
-        <v>1.6</v>
-      </c>
-      <c r="AE17">
-        <v>1.23</v>
       </c>
       <c r="AF17">
         <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="P19">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
         <v>2.45</v>
@@ -3451,7 +3451,7 @@
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD19">
         <v>1.12</v>
@@ -3460,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG19">
         <v>1.6</v>
@@ -3578,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.23</v>
@@ -3590,43 +3590,43 @@
         <v>3.42</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
         <v>1.12</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA20">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB20">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AC20">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD20">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE20">
         <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG20">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
         <v>2.13</v>
@@ -4909,7 +4909,7 @@
         <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA28">
         <v>1.12</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
         <v>1.44</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5872,10 +5872,10 @@
         <v>2.83</v>
       </c>
       <c r="U34">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5887,7 +5887,7 @@
         <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
         <v>2.04</v>
@@ -5902,13 +5902,13 @@
         <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1459,43 +1459,43 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R7">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="S7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T7">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V7">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
         <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z7">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA7">
         <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AC7">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AD7">
         <v>1.68</v>
@@ -1504,10 +1504,10 @@
         <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG7">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
         <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>3.93</v>
+        <v>3.56</v>
       </c>
       <c r="R8">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
         <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U8">
         <v>3.32</v>
@@ -1649,7 +1649,7 @@
         <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AA8">
         <v>2.27</v>
@@ -1661,16 +1661,16 @@
         <v>4.15</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q10">
         <v>3.08</v>
@@ -1984,10 +1984,10 @@
         <v>1.78</v>
       </c>
       <c r="AC10">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
@@ -2120,7 +2120,7 @@
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
         <v>2.59</v>
@@ -2144,19 +2144,19 @@
         <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC11">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AD11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
         <v>2.2</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q12">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R12">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2431,16 +2431,16 @@
         <v>1.28</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>8.44</v>
       </c>
       <c r="Q13">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R13">
-        <v>2.76</v>
+        <v>3.07</v>
       </c>
       <c r="S13">
         <v>1.18</v>
@@ -2449,19 +2449,19 @@
         <v>4.8</v>
       </c>
       <c r="U13">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
         <v>7.5</v>
@@ -2470,22 +2470,22 @@
         <v>1.34</v>
       </c>
       <c r="AB13">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AC13">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AD13">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE13">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AF13">
         <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="O14">
         <v>3.9</v>
       </c>
       <c r="P14">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
         <v>3.58</v>
       </c>
       <c r="R14">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2612,10 +2612,10 @@
         <v>3.34</v>
       </c>
       <c r="U14">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2627,16 +2627,16 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA14">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
         <v>1.57</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3898,13 +3898,13 @@
         <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="R22">
         <v>2.4</v>
@@ -3913,13 +3913,13 @@
         <v>1.19</v>
       </c>
       <c r="T22">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U22">
         <v>2.07</v>
       </c>
       <c r="V22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
         <v>1.15</v>
@@ -3940,16 +3940,16 @@
         <v>2.62</v>
       </c>
       <c r="AC22">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD22">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE22">
         <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG22">
         <v>2.62</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
         <v>1.7</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1148,10 +1148,10 @@
         <v>2.87</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1160,28 +1160,28 @@
         <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AA5">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AD5">
         <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.8</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O9">
         <v>3.25</v>
@@ -1785,46 +1785,46 @@
         <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
         <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
         <v>1.11</v>
@@ -2754,22 +2754,22 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
         <v>3.42</v>
@@ -2778,7 +2778,7 @@
         <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>1.5</v>
@@ -2799,7 +2799,7 @@
         <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -2808,10 +2808,10 @@
         <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
         <v>1.44</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="O16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Q16">
         <v>2.93</v>
@@ -2938,7 +2938,7 @@
         <v>4.5</v>
       </c>
       <c r="U16">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V16">
         <v>1.83</v>
@@ -2953,10 +2953,10 @@
         <v>1.08</v>
       </c>
       <c r="Z16">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="AA16">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB16">
         <v>3.08</v>
@@ -2971,7 +2971,7 @@
         <v>1.35</v>
       </c>
       <c r="AF16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG16">
         <v>3</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O22">
         <v>3.6</v>
@@ -3916,7 +3916,7 @@
         <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V22">
         <v>1.7</v>
@@ -3949,7 +3949,7 @@
         <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG22">
         <v>2.62</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.7</v>
@@ -4091,7 +4091,7 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
         <v>3.5</v>
@@ -4103,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD23">
         <v>1.38</v>
@@ -5368,10 +5368,10 @@
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="R31">
         <v>2.04</v>
@@ -5380,13 +5380,13 @@
         <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U31">
         <v>2.91</v>
       </c>
       <c r="V31">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
         <v>1.03</v>
@@ -5407,7 +5407,7 @@
         <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="AD31">
         <v>1.24</v>
@@ -5419,7 +5419,7 @@
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -647,34 +647,34 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.05</v>
+        <v>3.39</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -683,13 +683,13 @@
         <v>3.28</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG2">
         <v>1.89</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.28</v>
       </c>
       <c r="T3">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
         <v>1.4</v>
@@ -852,10 +852,10 @@
         <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O4">
+        <v>3.35</v>
+      </c>
+      <c r="P4">
         <v>3.4</v>
-      </c>
-      <c r="P4">
-        <v>3.2</v>
       </c>
       <c r="Q4">
         <v>2.45</v>
@@ -976,10 +976,10 @@
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -991,7 +991,7 @@
         <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.19</v>
@@ -1000,10 +1000,10 @@
         <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R7">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="S7">
         <v>1.17</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="U7">
         <v>1.83</v>
@@ -1483,19 +1483,19 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB7">
         <v>2.74</v>
       </c>
       <c r="AC7">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AD7">
         <v>1.68</v>
@@ -1504,10 +1504,10 @@
         <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="S8">
         <v>1.46</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AK8">
         <v>1.35</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
         <v>3.2</v>
@@ -1812,7 +1812,7 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
         <v>1.73</v>
@@ -1954,10 +1954,10 @@
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
         <v>2.77</v>
@@ -1969,7 +1969,7 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.27</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q12">
         <v>2.85</v>
@@ -2286,10 +2286,10 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2301,13 +2301,13 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
@@ -2322,7 +2322,7 @@
         <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="P13">
-        <v>8.44</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
         <v>1.62</v>
@@ -2443,10 +2443,10 @@
         <v>3.07</v>
       </c>
       <c r="S13">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="U13">
         <v>1.85</v>
@@ -2455,37 +2455,37 @@
         <v>1.85</v>
       </c>
       <c r="W13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB13">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AC13">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AE13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
         <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="O14">
         <v>3.9</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q14">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -2615,7 +2615,7 @@
         <v>2.17</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2630,13 +2630,13 @@
         <v>4.55</v>
       </c>
       <c r="AA14">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AD14">
         <v>1.57</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S17">
         <v>1.25</v>
@@ -3107,7 +3107,7 @@
         <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3119,25 +3119,25 @@
         <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
         <v>2.35</v>
       </c>
       <c r="AC17">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AD17">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB18">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3409,13 +3409,13 @@
         <v>1.75</v>
       </c>
       <c r="O19">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>4.85</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R19">
         <v>1.95</v>
@@ -3451,7 +3451,7 @@
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD19">
         <v>1.12</v>
@@ -3460,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
         <v>1.6</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK19">
         <v>1.91</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
         <v>2.5</v>
@@ -3587,43 +3587,43 @@
         <v>1.23</v>
       </c>
       <c r="T20">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V20">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AC20">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AD20">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.58</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
         <v>3.4</v>
       </c>
       <c r="P26">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q26">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4577,22 +4577,22 @@
         <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
         <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC26">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AD26">
         <v>1.27</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4728,13 +4728,13 @@
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U27">
         <v>2.95</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4746,7 +4746,7 @@
         <v>1.34</v>
       </c>
       <c r="Z27">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="O28">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P28">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>2.51</v>
+        <v>2.94</v>
       </c>
       <c r="R28">
         <v>2.99</v>
@@ -4894,10 +4894,10 @@
         <v>5.4</v>
       </c>
       <c r="U28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="W28">
         <v>1.36</v>
@@ -4906,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z28">
         <v>12</v>
@@ -4927,7 +4927,7 @@
         <v>1.75</v>
       </c>
       <c r="AF28">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AG28">
         <v>4.2</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AK28">
         <v>1.44</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>4.2</v>
@@ -5051,10 +5051,10 @@
         <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="U29">
         <v>3.1</v>
@@ -5066,31 +5066,31 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
         <v>1.38</v>
       </c>
       <c r="Z29">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG29">
         <v>1.77</v>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5531,28 +5531,28 @@
         <v>3.75</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
         <v>2</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -5561,28 +5561,28 @@
         <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB32">
         <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK32">
         <v>2.19</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
         <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T33">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="U33">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
+        <v>1.1</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1.27</v>
+      </c>
+      <c r="Z33">
+        <v>3.65</v>
+      </c>
+      <c r="AA33">
+        <v>1.87</v>
+      </c>
+      <c r="AB33">
+        <v>1.89</v>
+      </c>
+      <c r="AC33">
+        <v>3.2</v>
+      </c>
+      <c r="AD33">
+        <v>1.3</v>
+      </c>
+      <c r="AE33">
         <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
-        <v>3.6</v>
-      </c>
-      <c r="AA33">
-        <v>2</v>
-      </c>
-      <c r="AB33">
-        <v>1.86</v>
-      </c>
-      <c r="AC33">
-        <v>3.5</v>
-      </c>
-      <c r="AD33">
-        <v>1.28</v>
-      </c>
-      <c r="AE33">
-        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>2.96</v>
@@ -5863,13 +5863,13 @@
         <v>2.88</v>
       </c>
       <c r="R34">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S34">
         <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="U34">
         <v>2.7</v>
@@ -5887,7 +5887,7 @@
         <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
         <v>2.04</v>
@@ -5905,7 +5905,7 @@
         <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG34">
         <v>1.95</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O35">
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T35">
         <v>2.45</v>
@@ -6038,7 +6038,7 @@
         <v>3.25</v>
       </c>
       <c r="V35">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W35">
         <v>1.04</v>
@@ -6050,28 +6050,28 @@
         <v>1.45</v>
       </c>
       <c r="Z35">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AA35">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB35">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC35">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD35">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
         <v>2.25</v>
       </c>
       <c r="AG35">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -644,37 +644,37 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
         <v>2.69</v>
       </c>
       <c r="U2">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -686,7 +686,7 @@
         <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
         <v>1.77</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.28</v>
@@ -819,37 +819,37 @@
         <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.15</v>
+      </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
+      <c r="AA3">
+        <v>1.67</v>
+      </c>
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>2.66</v>
+      </c>
+      <c r="AD3">
+        <v>1.37</v>
+      </c>
+      <c r="AE3">
         <v>1.11</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.2</v>
-      </c>
-      <c r="Z3">
-        <v>4.33</v>
-      </c>
-      <c r="AA3">
-        <v>1.62</v>
-      </c>
-      <c r="AB3">
-        <v>2.15</v>
-      </c>
-      <c r="AC3">
-        <v>2.7</v>
-      </c>
-      <c r="AD3">
-        <v>1.4</v>
-      </c>
-      <c r="AE3">
-        <v>1.14</v>
       </c>
       <c r="AF3">
         <v>1.62</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK3">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="Q4">
         <v>2.45</v>
@@ -976,7 +976,7 @@
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
         <v>3.2</v>
@@ -1000,19 +1000,19 @@
         <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
         <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD4">
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>1.61</v>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O5">
         <v>3.25</v>
       </c>
       <c r="P5">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1139,13 +1139,13 @@
         <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="V5">
         <v>1.33</v>
@@ -1160,10 +1160,10 @@
         <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
         <v>1.67</v>
@@ -1175,13 +1175,13 @@
         <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
+        <v>3.35</v>
+      </c>
+      <c r="O8">
         <v>3.25</v>
       </c>
-      <c r="O8">
-        <v>3.2</v>
-      </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="Q8">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="R8">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="U8">
         <v>3.32</v>
@@ -1646,10 +1646,10 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AA8">
         <v>2.27</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.08</v>
@@ -1818,16 +1818,16 @@
         <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
         <v>1.33</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="R13">
-        <v>3.07</v>
+        <v>2.43</v>
       </c>
       <c r="S13">
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="V13">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>6.25</v>
+        <v>4.55</v>
       </c>
       <c r="AA13">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AB13">
-        <v>3.11</v>
+        <v>2.29</v>
       </c>
       <c r="AC13">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD13">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="P14">
-        <v>1.79</v>
+        <v>7.5</v>
       </c>
       <c r="Q14">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="R14">
-        <v>2.43</v>
+        <v>3.07</v>
       </c>
       <c r="S14">
         <v>1.22</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="U14">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>4.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA14">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AB14">
-        <v>2.29</v>
+        <v>3.11</v>
       </c>
       <c r="AC14">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
+        <v>1.92</v>
+      </c>
+      <c r="AE14">
+        <v>1.33</v>
+      </c>
+      <c r="AF14">
         <v>1.57</v>
       </c>
-      <c r="AE14">
-        <v>1.19</v>
-      </c>
-      <c r="AF14">
-        <v>1.51</v>
-      </c>
       <c r="AG14">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
         <v>2.48</v>
@@ -3454,13 +3454,13 @@
         <v>5.5</v>
       </c>
       <c r="AD19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG19">
         <v>1.6</v>
@@ -4103,13 +4103,13 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AD23">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.83</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
         <v>3.25</v>
@@ -4230,49 +4230,49 @@
         <v>2.75</v>
       </c>
       <c r="Q24">
+        <v>2.75</v>
+      </c>
+      <c r="R24">
+        <v>2.2</v>
+      </c>
+      <c r="S24">
+        <v>1.33</v>
+      </c>
+      <c r="T24">
         <v>3</v>
       </c>
-      <c r="R24">
-        <v>2.15</v>
-      </c>
-      <c r="S24">
-        <v>1.3</v>
-      </c>
-      <c r="T24">
-        <v>2.88</v>
-      </c>
       <c r="U24">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="V24">
         <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC24">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
         <v>1.64</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
         <v>1.57</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
         <v>3.4</v>
       </c>
       <c r="P26">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -4571,7 +4571,7 @@
         <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.04</v>
@@ -4583,13 +4583,13 @@
         <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC26">
         <v>3.35</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="P27">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4731,7 +4731,7 @@
         <v>2.65</v>
       </c>
       <c r="U27">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="V27">
         <v>1.33</v>
@@ -4743,7 +4743,7 @@
         <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z27">
         <v>2.95</v>
@@ -4761,7 +4761,7 @@
         <v>1.2</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
         <v>1.83</v>
@@ -4783,7 +4783,7 @@
         <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
         <v>2.94</v>
       </c>
       <c r="R28">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="S28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T28">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V28">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="W28">
         <v>1.36</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
         <v>1.44</v>
@@ -5039,7 +5039,7 @@
         <v>1.87</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
         <v>4.2</v>
@@ -5066,7 +5066,7 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
         <v>1.38</v>
@@ -5075,10 +5075,10 @@
         <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5093,7 +5093,7 @@
         <v>1.94</v>
       </c>
       <c r="AG29">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P30">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O31">
         <v>3.4</v>
@@ -5407,16 +5407,16 @@
         <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AD31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG31">
         <v>1.71</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O32">
         <v>3.75</v>
@@ -5537,7 +5537,7 @@
         <v>2</v>
       </c>
       <c r="R32">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
         <v>1.34</v>
@@ -5546,10 +5546,10 @@
         <v>2.95</v>
       </c>
       <c r="U32">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
         <v>1.06</v>
@@ -5567,7 +5567,7 @@
         <v>1.82</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC32">
         <v>2.92</v>
@@ -5579,7 +5579,7 @@
         <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG32">
         <v>1.87</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
         <v>2.19</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
         <v>2.1</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
         <v>2.93</v>
@@ -5724,7 +5724,7 @@
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA33">
         <v>1.87</v>
@@ -5739,13 +5739,13 @@
         <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="O35">
         <v>3.3</v>
@@ -6038,7 +6038,7 @@
         <v>3.25</v>
       </c>
       <c r="V35">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W35">
         <v>1.04</v>
@@ -6065,13 +6065,13 @@
         <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>2.25</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1818,10 +1818,10 @@
         <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AD9">
         <v>1.36</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O18">
         <v>2.45</v>
       </c>
       <c r="P18">
-        <v>4.26</v>
+        <v>4.46</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3412,10 +3412,10 @@
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
         <v>1.95</v>
@@ -3436,13 +3436,13 @@
         <v>1</v>
       </c>
       <c r="X19">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
         <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AA19">
         <v>2.5</v>
@@ -3451,7 +3451,7 @@
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD19">
         <v>1.14</v>
@@ -3460,10 +3460,10 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
         <v>1.91</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4728,10 +4728,10 @@
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U27">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="V27">
         <v>1.33</v>
@@ -4743,10 +4743,10 @@
         <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="O30">
         <v>3.33</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.58</v>
       </c>
       <c r="Q31">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="R31">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T31">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U31">
         <v>2.91</v>
@@ -5389,10 +5389,10 @@
         <v>1.32</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.38</v>
@@ -5407,19 +5407,19 @@
         <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AG31">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="R32">
         <v>2.13</v>
@@ -5543,10 +5543,10 @@
         <v>1.34</v>
       </c>
       <c r="T32">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="V32">
         <v>1.42</v>
@@ -5564,16 +5564,16 @@
         <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC32">
         <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
         <v>1.08</v>
@@ -5694,7 +5694,7 @@
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -5706,13 +5706,13 @@
         <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U33">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
         <v>1.1</v>
@@ -5727,13 +5727,13 @@
         <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD33">
         <v>1.3</v>
@@ -5742,10 +5742,10 @@
         <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.53</v>
       </c>
       <c r="AK33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O34">
         <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5866,7 +5866,7 @@
         <v>1.99</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
         <v>2.84</v>
@@ -5887,7 +5887,7 @@
         <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
         <v>2.04</v>
@@ -5905,10 +5905,10 @@
         <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
         <v>1.53</v>
@@ -6017,10 +6017,10 @@
         <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q35">
         <v>2.21</v>
@@ -6038,34 +6038,34 @@
         <v>3.25</v>
       </c>
       <c r="V35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W35">
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y35">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z35">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AA35">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AB35">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC35">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD35">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
         <v>2.25</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -644,10 +644,10 @@
         <v>3.34</v>
       </c>
       <c r="Q2">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -656,25 +656,25 @@
         <v>2.69</v>
       </c>
       <c r="U2">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
         <v>1.75</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>3.59</v>
+        <v>4.05</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="U3">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA3">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>3.42</v>
       </c>
       <c r="Q4">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -994,28 +994,28 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD4">
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
         <v>2.2</v>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U9">
         <v>2.47</v>
@@ -1806,28 +1806,28 @@
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AA9">
         <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC9">
         <v>2.89</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AK9">
         <v>1.33</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P16">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
         <v>2.6</v>
@@ -2938,37 +2938,37 @@
         <v>4.5</v>
       </c>
       <c r="U16">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V16">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
         <v>7.5</v>
       </c>
       <c r="AA16">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB16">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AC16">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD16">
         <v>1.91</v>
       </c>
       <c r="AE16">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF16">
         <v>1.33</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O24">
         <v>3.25</v>
       </c>
       <c r="P24">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S24">
         <v>1.33</v>
@@ -4242,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.05</v>
@@ -4254,28 +4254,28 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD24">
         <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
         <v>2.1</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
         <v>1.57</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4589,10 +4589,10 @@
         <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="AD26">
         <v>1.27</v>
@@ -4604,7 +4604,7 @@
         <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
@@ -5054,13 +5054,13 @@
         <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
         <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5075,7 +5075,7 @@
         <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
         <v>1.73</v>
@@ -5090,10 +5090,10 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P31">
-        <v>4.58</v>
+        <v>4.49</v>
       </c>
       <c r="Q31">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S31">
         <v>1.45</v>
@@ -5386,40 +5386,40 @@
         <v>2.91</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
         <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
         <v>1.38</v>
       </c>
       <c r="Z31">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>1.99</v>
       </c>
       <c r="AG31">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q3">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="S3">
         <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,28 +834,28 @@
         <v>1.14</v>
       </c>
       <c r="Z3">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC3">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AD3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
         <v>3.17</v>
       </c>
       <c r="Q5">
+        <v>2.49</v>
+      </c>
+      <c r="R5">
+        <v>2.06</v>
+      </c>
+      <c r="S5">
+        <v>1.42</v>
+      </c>
+      <c r="T5">
         <v>2.5</v>
       </c>
-      <c r="R5">
-        <v>2.05</v>
-      </c>
-      <c r="S5">
-        <v>1.4</v>
-      </c>
-      <c r="T5">
-        <v>2.73</v>
-      </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
         <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z5">
         <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AD5">
         <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
         <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1459,22 +1459,22 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="R7">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="S7">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="W7">
         <v>1.17</v>
@@ -1486,28 +1486,28 @@
         <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.55</v>
+        <v>5.2</v>
       </c>
       <c r="AA7">
         <v>1.33</v>
       </c>
       <c r="AB7">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AC7">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD7">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AE7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AG7">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK7">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="O8">
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="R8">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T8">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="U8">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -1646,7 +1646,7 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
         <v>2.81</v>
@@ -1655,7 +1655,7 @@
         <v>2.27</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC8">
         <v>4.15</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AK8">
         <v>1.26</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="Q10">
         <v>3.08</v>
@@ -1954,16 +1954,16 @@
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1975,22 +1975,22 @@
         <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
         <v>1.98</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC10">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="AD10">
         <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q11">
         <v>2.8</v>
@@ -2117,19 +2117,19 @@
         <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U11">
         <v>2.59</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,25 +2141,25 @@
         <v>3.75</v>
       </c>
       <c r="AA11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="Q12">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AC13">
         <v>2.43</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE13">
         <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
         <v>2.39</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O14">
         <v>5.3</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R14">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T14">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W14">
         <v>1.17</v>
@@ -2624,31 +2624,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z14">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA14">
         <v>1.35</v>
       </c>
       <c r="AB14">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AC14">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD14">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q15">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="R15">
         <v>2.4</v>
@@ -2772,10 +2772,10 @@
         <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V15">
         <v>1.63</v>
@@ -2787,19 +2787,19 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB15">
         <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -3086,58 +3086,58 @@
         <v>3.8</v>
       </c>
       <c r="P17">
-        <v>4.6</v>
+        <v>4.86</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="R17">
         <v>2.55</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC17">
-        <v>2.57</v>
+        <v>2.28</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
         <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK17">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O18">
         <v>2.45</v>
       </c>
       <c r="P18">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3412,10 +3412,10 @@
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>1.95</v>
@@ -3439,31 +3439,31 @@
         <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA19">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB19">
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF19">
         <v>2.25</v>
       </c>
       <c r="AG19">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,25 +3578,25 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
         <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
         <v>3.75</v>
       </c>
       <c r="U20">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="V20">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3605,25 +3605,25 @@
         <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
         <v>2.55</v>
       </c>
       <c r="AC20">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE20">
         <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
         <v>2.15</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK20">
         <v>2.6</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="Q22">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
         <v>1.19</v>
@@ -3916,7 +3916,7 @@
         <v>3.9</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V22">
         <v>1.7</v>
@@ -3928,7 +3928,7 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
@@ -3940,35 +3940,35 @@
         <v>2.62</v>
       </c>
       <c r="AC22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD22">
+        <v>1.7</v>
+      </c>
+      <c r="AE22">
+        <v>1.25</v>
+      </c>
+      <c r="AF22">
+        <v>1.4</v>
+      </c>
+      <c r="AG22">
+        <v>2.75</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.2</v>
+      </c>
+      <c r="AK22">
         <v>1.67</v>
-      </c>
-      <c r="AE22">
-        <v>1.29</v>
-      </c>
-      <c r="AF22">
-        <v>1.39</v>
-      </c>
-      <c r="AG22">
-        <v>2.62</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.25</v>
-      </c>
-      <c r="AK22">
-        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>5.14</v>
       </c>
       <c r="Q23">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U23">
         <v>2.59</v>
@@ -4085,34 +4085,34 @@
         <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
         <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
         <v>2.95</v>
       </c>
       <c r="AD23">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG23">
         <v>1.85</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
         <v>2.3</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P27">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4731,13 +4731,13 @@
         <v>2.62</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.04</v>
@@ -4746,13 +4746,13 @@
         <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AA27">
         <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
         <v>3.68</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="R28">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S28">
         <v>1.11</v>
@@ -4894,7 +4894,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V28">
         <v>2.21</v>
@@ -4906,31 +4906,31 @@
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA28">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AB28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AC28">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AD28">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AE28">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AF28">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AG28">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,49 +5036,49 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
         <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
         <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
         <v>3.8</v>
@@ -5090,10 +5090,10 @@
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="O30">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>1.7</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q32">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="U32">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -5570,19 +5570,19 @@
         <v>1.93</v>
       </c>
       <c r="AC32">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AD32">
         <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG32">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O33">
         <v>3.3</v>
@@ -5697,7 +5697,7 @@
         <v>2.16</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
         <v>2.13</v>
@@ -5709,43 +5709,43 @@
         <v>2.95</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
         <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
         <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC33">
         <v>2.97</v>
       </c>
       <c r="AD33">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
         <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AK33">
         <v>1.36</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5866,13 +5866,13 @@
         <v>1.99</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5884,31 +5884,31 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AA34">
         <v>2.04</v>
       </c>
       <c r="AB34">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC34">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AK34">
         <v>1.53</v>
@@ -6017,13 +6017,13 @@
         <v>1.65</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q35">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="R35">
         <v>2</v>
@@ -6035,37 +6035,37 @@
         <v>2.45</v>
       </c>
       <c r="U35">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V35">
         <v>1.3</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.09</v>
       </c>
       <c r="Y35">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z35">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA35">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AB35">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AC35">
         <v>4</v>
       </c>
       <c r="AD35">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>2.25</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P21">
-        <v>1.89</v>
+        <v>2.87</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>2.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q22">
-        <v>2.52</v>
+        <v>3.61</v>
       </c>
       <c r="R22">
+        <v>2.32</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
+        <v>3.36</v>
+      </c>
+      <c r="U22">
+        <v>2.25</v>
+      </c>
+      <c r="V22">
+        <v>1.59</v>
+      </c>
+      <c r="W22">
+        <v>1.12</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.15</v>
+      </c>
+      <c r="Z22">
+        <v>5</v>
+      </c>
+      <c r="AA22">
+        <v>1.53</v>
+      </c>
+      <c r="AB22">
+        <v>2.4</v>
+      </c>
+      <c r="AC22">
+        <v>2.3</v>
+      </c>
+      <c r="AD22">
+        <v>1.57</v>
+      </c>
+      <c r="AE22">
+        <v>1.22</v>
+      </c>
+      <c r="AF22">
+        <v>1.44</v>
+      </c>
+      <c r="AG22">
         <v>2.5</v>
       </c>
-      <c r="S22">
-        <v>1.19</v>
-      </c>
-      <c r="T22">
-        <v>3.9</v>
-      </c>
-      <c r="U22">
-        <v>2.05</v>
-      </c>
-      <c r="V22">
-        <v>1.7</v>
-      </c>
-      <c r="W22">
-        <v>1.15</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.12</v>
-      </c>
-      <c r="Z22">
-        <v>5.5</v>
-      </c>
-      <c r="AA22">
-        <v>1.38</v>
-      </c>
-      <c r="AB22">
-        <v>2.62</v>
-      </c>
-      <c r="AC22">
-        <v>2.1</v>
-      </c>
-      <c r="AD22">
-        <v>1.7</v>
-      </c>
-      <c r="AE22">
-        <v>1.25</v>
-      </c>
-      <c r="AF22">
-        <v>1.4</v>
-      </c>
-      <c r="AG22">
-        <v>2.75</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q7">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R7">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="V7">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z7">
         <v>5.2</v>
       </c>
       <c r="AA7">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC7">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE7">
         <v>1.3</v>
       </c>
       <c r="AF7">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK7">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="O8">
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="R8">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="S8">
         <v>1.47</v>
       </c>
       <c r="T8">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="U8">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -1643,7 +1643,7 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.36</v>
@@ -1655,10 +1655,10 @@
         <v>2.27</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
         <v>1.18</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AK8">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,40 +1779,40 @@
         <v>3.01</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="P9">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA9">
         <v>1.73</v>
@@ -1821,19 +1821,19 @@
         <v>2</v>
       </c>
       <c r="AC9">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AK9">
         <v>1.33</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="Q10">
         <v>3.08</v>
@@ -1954,13 +1954,13 @@
         <v>1.98</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
         <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
         <v>1.38</v>
@@ -1978,13 +1978,13 @@
         <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB10">
         <v>1.82</v>
       </c>
       <c r="AC10">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="AD10">
         <v>1.29</v>
@@ -1993,10 +1993,10 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="Q11">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R11">
         <v>2.2</v>
@@ -2120,46 +2120,46 @@
         <v>1.34</v>
       </c>
       <c r="T11">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="U11">
         <v>2.59</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB11">
         <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE11">
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2286,43 +2286,43 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
         <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="O13">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q13">
         <v>3.75</v>
       </c>
       <c r="R13">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U13">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
         <v>1.57</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1.03</v>
@@ -2485,7 +2485,7 @@
         <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2594,22 +2594,22 @@
         <v>1.3</v>
       </c>
       <c r="O14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="P14">
-        <v>9.550000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q14">
         <v>1.67</v>
       </c>
       <c r="R14">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="S14">
         <v>1.18</v>
       </c>
       <c r="T14">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
         <v>1.91</v>
@@ -2618,7 +2618,7 @@
         <v>1.8</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,28 +2627,28 @@
         <v>1.06</v>
       </c>
       <c r="Z14">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
         <v>3.1</v>
       </c>
       <c r="AC14">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AD14">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -635,61 +635,61 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O2">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="Q2">
         <v>2.7</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.08</v>
+        <v>3.39</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
         <v>1.89</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="O3">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q3">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U3">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC3">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.18</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
         <v>2.91</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.09</v>
@@ -994,31 +994,31 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB4">
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK4">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,66 +1116,66 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="R5">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
         <v>1.03</v>
       </c>
       <c r="X5">
+        <v>1.08</v>
+      </c>
+      <c r="Y5">
+        <v>1.4</v>
+      </c>
+      <c r="Z5">
+        <v>2.75</v>
+      </c>
+      <c r="AA5">
+        <v>2.15</v>
+      </c>
+      <c r="AB5">
+        <v>1.65</v>
+      </c>
+      <c r="AC5">
+        <v>3.9</v>
+      </c>
+      <c r="AD5">
+        <v>1.2</v>
+      </c>
+      <c r="AE5">
         <v>1.06</v>
-      </c>
-      <c r="Y5">
-        <v>1.34</v>
-      </c>
-      <c r="Z5">
-        <v>2.9</v>
-      </c>
-      <c r="AA5">
-        <v>2.18</v>
-      </c>
-      <c r="AB5">
-        <v>1.66</v>
-      </c>
-      <c r="AC5">
-        <v>3.76</v>
-      </c>
-      <c r="AD5">
-        <v>1.19</v>
-      </c>
-      <c r="AE5">
-        <v>1.03</v>
       </c>
       <c r="AF5">
         <v>1.93</v>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "82", "90+4"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="P7">
         <v>12</v>
@@ -1462,7 +1462,7 @@
         <v>1.46</v>
       </c>
       <c r="R7">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="S7">
         <v>1.22</v>
@@ -1477,13 +1477,13 @@
         <v>1.66</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
         <v>5.2</v>
@@ -1492,22 +1492,22 @@
         <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD7">
         <v>1.73</v>
       </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF7">
         <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1619,22 +1619,22 @@
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="R8">
         <v>2.12</v>
       </c>
       <c r="S8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="U8">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
         <v>2.56</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1812,7 +1812,7 @@
         <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA9">
         <v>1.73</v>
@@ -1821,19 +1821,19 @@
         <v>2</v>
       </c>
       <c r="AC9">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AK9">
         <v>1.33</v>
@@ -1945,13 +1945,13 @@
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="Q10">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="R10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
         <v>1.4</v>
@@ -1978,10 +1978,10 @@
         <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB10">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
         <v>3.61</v>
@@ -1990,13 +1990,13 @@
         <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK10">
         <v>1.5</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
         <v>3.65</v>
       </c>
       <c r="P11">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>2.63</v>
@@ -2147,7 +2147,7 @@
         <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AD11">
         <v>1.39</v>
@@ -2156,7 +2156,7 @@
         <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG11">
         <v>2.18</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q13">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R13">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
         <v>2.2</v>
@@ -2458,7 +2458,7 @@
         <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2467,25 +2467,25 @@
         <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AC13">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="AD13">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE13">
         <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O14">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>1.67</v>
       </c>
       <c r="R14">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="S14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U14">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V14">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z14">
-        <v>6.05</v>
+        <v>5.6</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB14">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AD14">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.01</v>
+        <v>3.16</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U15">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2787,19 +2787,19 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -2811,7 +2811,7 @@
         <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK15">
         <v>1.44</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R16">
         <v>2.6</v>
@@ -2938,31 +2938,31 @@
         <v>4.5</v>
       </c>
       <c r="U16">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V16">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z16">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA16">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB16">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="AC16">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD16">
         <v>1.91</v>
@@ -2971,26 +2971,26 @@
         <v>1.32</v>
       </c>
       <c r="AF16">
+        <v>1.32</v>
+      </c>
+      <c r="AG16">
+        <v>2.9</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.85</v>
+      </c>
+      <c r="AK16">
         <v>1.33</v>
-      </c>
-      <c r="AG16">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.21</v>
-      </c>
-      <c r="AK16">
-        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>4.86</v>
+        <v>4.97</v>
       </c>
       <c r="Q17">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
         <v>1.29</v>
@@ -3101,43 +3101,43 @@
         <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AB17">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
         <v>2.28</v>
       </c>
       <c r="AD17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
         <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="O18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="P18">
-        <v>4.36</v>
+        <v>3.94</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3412,19 +3412,19 @@
         <v>3.2</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
         <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
         <v>3.5</v>
@@ -3442,7 +3442,7 @@
         <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AA19">
         <v>2.6</v>
@@ -3451,13 +3451,13 @@
         <v>1.43</v>
       </c>
       <c r="AC19">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.25</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q20">
         <v>1.85</v>
@@ -3587,13 +3587,13 @@
         <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U20">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
         <v>1.11</v>
@@ -3608,7 +3608,7 @@
         <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB20">
         <v>2.55</v>
@@ -3620,7 +3620,7 @@
         <v>1.64</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
         <v>1.64</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK20">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="Q21">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
         <v>1.19</v>
       </c>
       <c r="T21">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="U21">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
         <v>1.7</v>
@@ -3771,10 +3771,10 @@
         <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB21">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AC21">
         <v>2.1</v>
@@ -3789,7 +3789,7 @@
         <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q22">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="R22">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
+        <v>1.13</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
         <v>1.12</v>
       </c>
-      <c r="X22">
-        <v>1.03</v>
-      </c>
-      <c r="Y22">
-        <v>1.15</v>
-      </c>
       <c r="Z22">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA22">
         <v>1.53</v>
@@ -3940,19 +3940,19 @@
         <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD22">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>5.14</v>
+        <v>4.65</v>
       </c>
       <c r="Q23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U23">
         <v>2.59</v>
@@ -4091,10 +4091,10 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
         <v>1.75</v>
@@ -4106,13 +4106,13 @@
         <v>2.95</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG23">
         <v>1.85</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="R24">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
         <v>1.33</v>
@@ -4242,37 +4242,37 @@
         <v>3</v>
       </c>
       <c r="U24">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD24">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.67</v>
@@ -4294,7 +4294,7 @@
         <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4571,7 +4571,7 @@
         <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
         <v>1.04</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
         <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB26">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
         <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q29">
         <v>2.45</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
+        <v>1.05</v>
+      </c>
+      <c r="X29">
         <v>1.07</v>
       </c>
-      <c r="X29">
-        <v>1.03</v>
-      </c>
       <c r="Y29">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z29">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AC29">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,49 +5362,49 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
         <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T31">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
         <v>2.91</v>
       </c>
       <c r="V31">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
         <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z31">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
         <v>4</v>
@@ -5416,10 +5416,10 @@
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>

--- a/jogos_2026-08-10.xlsx
+++ b/jogos_2026-08-10.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -778,23 +778,23 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -864,7 +864,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "46"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "83", "89"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "28", "36", "45+2", "53", "75"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "22"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "90+4"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,100 +2242,100 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AC12">
         <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "29", "85"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK12">
         <v>1.57</v>
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "23"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "28"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2743,14 +2743,14 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "51", "73"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "44", "90+3"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,23 +3060,23 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "77"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3232,14 +3232,14 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "33", "45+1", "58"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3700,139 +3700,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="O21">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
+        <v>3.8</v>
+      </c>
+      <c r="R21">
+        <v>2.45</v>
+      </c>
+      <c r="S21">
+        <v>1.22</v>
+      </c>
+      <c r="T21">
+        <v>3.8</v>
+      </c>
+      <c r="U21">
+        <v>2.23</v>
+      </c>
+      <c r="V21">
+        <v>1.6</v>
+      </c>
+      <c r="W21">
+        <v>1.13</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>1.12</v>
+      </c>
+      <c r="Z21">
+        <v>4.7</v>
+      </c>
+      <c r="AA21">
+        <v>1.53</v>
+      </c>
+      <c r="AB21">
+        <v>2.4</v>
+      </c>
+      <c r="AC21">
+        <v>2.27</v>
+      </c>
+      <c r="AD21">
+        <v>1.6</v>
+      </c>
+      <c r="AE21">
+        <v>1.2</v>
+      </c>
+      <c r="AF21">
+        <v>1.48</v>
+      </c>
+      <c r="AG21">
         <v>2.47</v>
       </c>
-      <c r="R21">
-        <v>2.4</v>
-      </c>
-      <c r="S21">
-        <v>1.19</v>
-      </c>
-      <c r="T21">
-        <v>3.86</v>
-      </c>
-      <c r="U21">
-        <v>2.06</v>
-      </c>
-      <c r="V21">
-        <v>1.7</v>
-      </c>
-      <c r="W21">
-        <v>1.15</v>
-      </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.11</v>
-      </c>
-      <c r="Z21">
-        <v>5.75</v>
-      </c>
-      <c r="AA21">
-        <v>1.39</v>
-      </c>
-      <c r="AB21">
-        <v>2.59</v>
-      </c>
-      <c r="AC21">
-        <v>2.1</v>
-      </c>
-      <c r="AD21">
-        <v>1.67</v>
-      </c>
-      <c r="AE21">
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>["19", "82", "90"]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>["38", "61"]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.25</v>
       </c>
-      <c r="AF21">
-        <v>1.4</v>
-      </c>
-      <c r="AG21">
-        <v>2.65</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.22</v>
-      </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3863,19 +3863,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3887,115 +3887,115 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>1.86</v>
+        <v>2.73</v>
       </c>
       <c r="Q22">
-        <v>3.8</v>
+        <v>2.47</v>
       </c>
       <c r="R22">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
+        <v>1.19</v>
+      </c>
+      <c r="T22">
+        <v>3.86</v>
+      </c>
+      <c r="U22">
+        <v>2.06</v>
+      </c>
+      <c r="V22">
+        <v>1.7</v>
+      </c>
+      <c r="W22">
+        <v>1.15</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.11</v>
+      </c>
+      <c r="Z22">
+        <v>5.75</v>
+      </c>
+      <c r="AA22">
+        <v>1.39</v>
+      </c>
+      <c r="AB22">
+        <v>2.59</v>
+      </c>
+      <c r="AC22">
+        <v>2.1</v>
+      </c>
+      <c r="AD22">
+        <v>1.67</v>
+      </c>
+      <c r="AE22">
+        <v>1.25</v>
+      </c>
+      <c r="AF22">
+        <v>1.4</v>
+      </c>
+      <c r="AG22">
+        <v>2.65</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>["82"]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.22</v>
       </c>
-      <c r="T22">
-        <v>3.8</v>
-      </c>
-      <c r="U22">
-        <v>2.23</v>
-      </c>
-      <c r="V22">
-        <v>1.6</v>
-      </c>
-      <c r="W22">
-        <v>1.13</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.12</v>
-      </c>
-      <c r="Z22">
-        <v>4.7</v>
-      </c>
-      <c r="AA22">
-        <v>1.53</v>
-      </c>
-      <c r="AB22">
-        <v>2.4</v>
-      </c>
-      <c r="AC22">
-        <v>2.27</v>
-      </c>
-      <c r="AD22">
-        <v>1.6</v>
-      </c>
-      <c r="AE22">
-        <v>1.2</v>
-      </c>
-      <c r="AF22">
-        <v>1.48</v>
-      </c>
-      <c r="AG22">
-        <v>2.47</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.25</v>
-      </c>
       <c r="AK22">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "28", "39"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "90+3"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="O27">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4731,16 +4731,16 @@
         <v>2.62</v>
       </c>
       <c r="U27">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="V27">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.36</v>
@@ -4749,25 +4749,25 @@
         <v>2.95</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
         <v>1.65</v>
       </c>
       <c r="AC27">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="AD27">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG27">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
         <v>1.44</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q28">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="S28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V28">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="W28">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X28">
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA28">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AB28">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AC28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AD28">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="AE28">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AF28">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AG28">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.15</v>
       </c>
       <c r="AK28">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
         <v>3.1</v>
@@ -5045,37 +5045,37 @@
         <v>4.8</v>
       </c>
       <c r="Q29">
+        <v>2.62</v>
+      </c>
+      <c r="R29">
+        <v>1.95</v>
+      </c>
+      <c r="S29">
+        <v>1.5</v>
+      </c>
+      <c r="T29">
         <v>2.45</v>
       </c>
-      <c r="R29">
-        <v>2</v>
-      </c>
-      <c r="S29">
-        <v>1.44</v>
-      </c>
-      <c r="T29">
-        <v>2.6</v>
-      </c>
       <c r="U29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
         <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
         <v>2.43</v>
       </c>
       <c r="AA29">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB29">
         <v>1.44</v>
@@ -5084,13 +5084,13 @@
         <v>5</v>
       </c>
       <c r="AD29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF29">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG29">
         <v>1.65</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
         <v>2.06</v>
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>1.96</v>
+      </c>
+      <c r="AC30">
+        <v>3.11</v>
+      </c>
+      <c r="AD30">
+        <v>1.36</v>
+      </c>
+      <c r="AE30">
+        <v>1.13</v>
+      </c>
+      <c r="AF30">
+        <v>1.67</v>
+      </c>
+      <c r="AG30">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.95</v>
       </c>
-      <c r="AB30">
-        <v>1.85</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
         <v>4.6</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R31">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U31">
-        <v>2.91</v>
+        <v>3.38</v>
       </c>
       <c r="V31">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
         <v>1.03</v>
@@ -5398,13 +5398,13 @@
         <v>1.42</v>
       </c>
       <c r="Z31">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC31">
         <v>4</v>
@@ -5416,10 +5416,10 @@
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG31">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
         <v>2</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
-        <v>4.33</v>
+        <v>5.23</v>
       </c>
       <c r="Q32">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O33">
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R33">
         <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y33">
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC33">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
       </c>
       <c r="R34">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S34">
         <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5884,31 +5884,31 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.38</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="U35">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="V35">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA35">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="AB35">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AC35">
         <v>4</v>
       </c>
       <c r="AD35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL35">
         <v>0</v>
